--- a/Result/checksun_type/預拌混凝土.xlsx
+++ b/Result/checksun_type/預拌混凝土.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>91.75999999999999</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>92.9</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>92.14</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>92.14</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>516.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>384.6</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>384.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>496.3</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>859.18</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>859.1799999999999</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-174.7880822545252</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>516</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>516.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>91.8</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>93.0</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>92.13</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>93</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>92.13</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>564.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>328.2</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>328.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>544.1</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>859.96</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>859.96</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-184.6450459226064</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>564</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>564.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>91.98</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>93.08</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>92.13</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>93.08</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>92.13</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>464.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>327.8</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>327.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>970.9</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>861.72</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>861.72</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-197.2748138083437</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>464</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>464.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>91.94</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>93.12</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>92.14</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>93.12</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>92.14</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>183.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>458.6</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>458.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>1459.3</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>858.08</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>858.08</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-197.5575245805275</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>183</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>183.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>91.82000000000001</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>93.14</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>92.14</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>93.14</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>92.14</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>196.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>554.6</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>554.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>1742.8</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>858.94</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>858.9400000000001</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-160.7986283771995</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>196</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>196.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>91.8</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>93.16</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>92.16</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>93.16</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>92.16</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>234.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>608.0</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>608</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>1776.1</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>858.76</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>858.76</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-103.9359685018312</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>234</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>234.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>91.6</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>93.16</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>92.17</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>93.16</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>92.17</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>562.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>760.0</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>760</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>1873.7</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>870.8</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>870.8</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-23.06302694766805</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>562</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>562.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>91.14000000000001</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>93.12</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>92.17</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>93.12</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>92.17</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>1118.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>1614.0</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>1614</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>1863.3</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>872.58</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>872.58</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>58.15056909212444</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>1118</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>1118.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>91.04</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>93.12</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>92.2</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>93.12</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>92.2</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>663.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>2460.0</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>2460</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>1866.6</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>863.18</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>863.1799999999999</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>112.5217573956809</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>663</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>663.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>91.52000000000001</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>93.15</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>92.22</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>93.15000000000001</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>92.22</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>463.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>2931.0</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>2931</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>1842.7</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>885.96</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>885.96</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>234.9262493509159</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>463</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>463.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>92.44000000000001</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>93.12</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>92.27</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>93.12</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>92.27</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>994.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>2944.2</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>2944.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>1865.9</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>888.28</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>888.28</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>422.8281575244332</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>994</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>994.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>35.28</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>35.74</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>35.54</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>35.74</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>35.54</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>91599502.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>75460731.2</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>75460731.2</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>70404844.4</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>78313378.72</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>78313378.72</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>1431964.60549283</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>91599502</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>91599502.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>35.09999999999999</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>35.76</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>35.54</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>35.76</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>35.54</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>92571320.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>66228759.8</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>66228759.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>71141343.5</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>79012327.72</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>79012327.72</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-177029.0214689672</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>92571320</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>92571320.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>35.04</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>35.81</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>35.57</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>35.81</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>35.57</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>67537221.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>58484079.4</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>58484079.4</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>68271036.2</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>79033378.64</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>79033378.64</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-2573392.237790503</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>67537221</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>67537221.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>34.98</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>35.83</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>35.6</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>35.83</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>35.6</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>62971881.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>65763948.6</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>65763948.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>65513016.8</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>78747672.26</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>78747672.26000001</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-3222636.502614461</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>62971881</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>62971881.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>35.08</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>35.86</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>35.64</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>35.86</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>35.64</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>62623732.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>66384034.2</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>66384034.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>64278849.0</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>78954828.14</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>78954828.14</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-3545890.577269591</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>62623732</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>62623732.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>35.23999999999999</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>35.88</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>35.67</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>35.88</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>35.67</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>45439645.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>65348957.6</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>65348957.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>63351678.2</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>79779068.28</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>79779068.28</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-3843741.484731585</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>45439645</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>45439645.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>35.55</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>35.91</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>35.73</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>35.91</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>35.73</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>53847918.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>76053927.2</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>76053927.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>63087662.1</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>81864848.4</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>81864848.40000001</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-2290814.120936871</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>53847918</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>53847918.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>35.81</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>35.88</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>35.77</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>35.88</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>35.77</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>103936567.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>78057993.0</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>78057993</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>64606481.6</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>81919545.82</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>81919545.81999999</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-891418.0611966699</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>103936567</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>103936567.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>36.09</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>35.82</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>35.8</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>35.82</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>35.8</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>66072309.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>65262085.0</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>65262085</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>61460703.1</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>81036708.82</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>81036708.81999999</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-4227085.437953666</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>66072309</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>66072309.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>36.28</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>35.74</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>35.82</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>35.74</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>35.82</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>57448349.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>62173663.8</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>62173663.8</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>63382255.3</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>80972289.34</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>80972289.34</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-4784472.42482245</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>57448349</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>57448349.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>36.39</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>35.62</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>35.85</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>35.62</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>35.85</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>98964493.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>61354398.8</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>61354398.8</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>63689956.1</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>80922325.8</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>80922325.8</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-4485869.819462776</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>98964493</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>98964493.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>15.5</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>15.51</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>15.61</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>15.51</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>15.61</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>1529519.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>1211570.2</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>1211570.2</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>1455383.2</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>1488562.2</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>1488562.2</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>7424.0549043559</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>1529519</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>1529519.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>15.44</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>15.51</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>15.61</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>15.51</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>15.61</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>552889.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>1531761.2</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>1531761.2</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>1383918.3</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>1525316.78</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>1525316.78</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-11250.54924079753</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>552889</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>552889.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>15.45</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>15.52</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>15.62</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>15.52</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>15.62</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>1602674.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>1702430.6</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>1702430.6</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>1381594.1</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>1543293.42</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>1543293.42</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>67112.17873901175</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>1602674</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>1602674.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>15.48</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>15.53</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>15.62</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>15.53</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>15.62</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>1670308.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>1614423.2</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>1614423.2</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>1303882.4</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>1523738.54</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>1523738.54</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>64185.10518377437</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>1670308</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>1670308.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>15.54</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>15.54</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>15.63</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>15.54</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>15.63</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>702461.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>1603478.4</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>1603478.4</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>1184677.9</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>1500194.58</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>1500194.58</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>50464.74634830048</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>702461</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>702461.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>15.58</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>15.56</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>15.64</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>15.64</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>3130474.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>1699196.2</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>1699196.2</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>1213694.9</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>1492008.92</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>1492008.92</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>132759.8142137555</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>3130474</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>3130474.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>15.61</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>15.57</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>15.66</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>15.57</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>15.66</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>1406236.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>1236075.4</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>1236075.4</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>1008882.6</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>1439500.94</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>1439500.94</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-14561.47505751392</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>1406236</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>1406236.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>15.59</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>15.57</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>15.66</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>15.57</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>15.66</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>1162637.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>1060757.6</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>1060757.6</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>930042.8</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>1427734.98</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>1427734.98</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-39760.62133584497</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>1162637</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>1162637.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>15.55</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>15.57</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>15.67</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>15.57</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>15.67</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>1615584.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>993341.6</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>993341.6</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>948198.5</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>1422825.74</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>1422825.74</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-48239.48668575194</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>1615584</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>1615584.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>15.49</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>15.56</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>15.67</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>15.67</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>1181050.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>765877.4</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>765877.4</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>1338803.9</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>1439931.86</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>1439931.86</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-107159.3483754136</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>1181050</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>1181050.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>15.47</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>15.55</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>15.67</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>15.67</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>814870.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>728193.6</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>728193.6</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>1376350.4</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>1469097.32</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>1469097.32</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-140946.2454900942</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>814870</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>814870.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>14.99</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>14.96</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>15.01</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>14.96</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>15.01</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>2296179.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>1772771.2</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>1772771.2</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>2871804.4</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>2127351.9</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>2127351.9</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-113079.6313257013</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>2296179</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>2296179.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>14.96</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>14.96</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>15.01</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>14.96</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>15.01</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>2724161.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>1588940.0</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>1588940</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>2969573.5</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>2187633.46</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>2187633.46</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-124878.8330158251</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>2724161</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>2724161.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,21 +16107,17 @@
           <t>14.95</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>14.96</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
+      <c r="AM37" t="n">
+        <v>14.96</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>15.01</v>
+      </c>
+      <c r="AO37" t="inlineStr">
         <is>
           <t>15.01</t>
         </is>
       </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>15.01</t>
-        </is>
-      </c>
       <c r="AP37" t="inlineStr">
         <is>
           <t>32.29</t>
@@ -16372,20 +16158,16 @@
           <t>1090295.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>1616637.4</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>1616637.4</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>2881734.2</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>2369216.76</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>2369216.76</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-183130.0913940081</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>1090295</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>1090295.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>14.95</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>14.96</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>15.02</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>14.96</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>15.02</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>1497444.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>2212682.4</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>2212682.4</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>3107504.3</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>2380023.54</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>2380023.54</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-84748.74295591237</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>1497444</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>1497444.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>14.98</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>14.96</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>15.03</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>14.96</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>15.03</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>1255777.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>3689238.2</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>3689238.2</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>3145706.7</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>2414310.08</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>2414310.08</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>15199.67420407897</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>1255777</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>1255777.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>14.99</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>14.96</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>15.04</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>14.96</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>15.04</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>1377023.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>3970837.6</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>3970837.6</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>3186018.9</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>2461469.72</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>2461469.72</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>183333.1746396348</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>1377023</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>1377023.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,21 +17827,17 @@
           <t>15.0</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
+      <c r="AM41" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>15.05</v>
+      </c>
+      <c r="AO41" t="inlineStr">
         <is>
           <t>14.97</t>
         </is>
       </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>15.05</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>14.97</t>
-        </is>
-      </c>
       <c r="AP41" t="inlineStr">
         <is>
           <t>48.84</t>
@@ -18116,20 +17878,16 @@
           <t>2862648.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>4350207.0</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>4350207</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>3555590.5</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>2528642.34</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>2528642.34</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>403985.6333104419</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>2862648</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>2862648.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,21 +18257,17 @@
           <t>15.0</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
+      <c r="AM42" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>15.06</v>
+      </c>
+      <c r="AO42" t="inlineStr">
         <is>
           <t>14.97</t>
         </is>
       </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>15.06</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>14.97</t>
-        </is>
-      </c>
       <c r="AP42" t="inlineStr">
         <is>
           <t>61.87</t>
@@ -18552,20 +18308,16 @@
           <t>4070520.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>4146831.0</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>4146831</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>3375587.6</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>2521002.36</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>2521002.36</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>545601.2659362219</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>4070520</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>4070520.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>14.98</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>14.97</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>15.06</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>15.06</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>8880223.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>4002326.2</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>4002326.2</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>3146122.9</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>2462772.2</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>2462772.2</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>599008.6959039001</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>8880223</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>8880223.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,21 +19117,17 @@
           <t>14.96</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
+      <c r="AM44" t="n">
+        <v>14.96</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>15.07</v>
+      </c>
+      <c r="AO44" t="inlineStr">
         <is>
           <t>14.96</t>
         </is>
       </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>15.07</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>14.96</t>
-        </is>
-      </c>
       <c r="AP44" t="inlineStr">
         <is>
           <t>24.37</t>
@@ -19424,20 +19168,16 @@
           <t>2663774.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>2602175.2</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>2602175.2</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>2428155.7</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>2387559.66</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>2387559.66</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>138586.5352897295</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>2663774</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>2663774.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,21 +19547,17 @@
           <t>14.95</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
+      <c r="AM45" t="n">
+        <v>14.96</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>15.07</v>
+      </c>
+      <c r="AO45" t="inlineStr">
         <is>
           <t>14.96</t>
         </is>
       </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>15.07</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>14.96</t>
-        </is>
-      </c>
       <c r="AP45" t="inlineStr">
         <is>
           <t>10.98</t>
@@ -19860,20 +19598,16 @@
           <t>3273870.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>2401200.2</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>2401200.2</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>2370937.2</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>2438206.8</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>2438206.8</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>141939.1795805674</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>3273870</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>3273870.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>31.11</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>30.78</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>30.76</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>30.78</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>30.76</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>55828580.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>35137088.6</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>35137088.6</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>30862720.3</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>38981141.32</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>38981141.32</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>2634689.975051943</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>55828580</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>55828580.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>30.67</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>30.76</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>30.73</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>30.76</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>30.73</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>35680080.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>25875732.2</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>25875732.2</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>26374450.5</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>43918565.22</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>43918565.22</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>602742.2985018045</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>35680080</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>35680080.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>30.3</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>30.78</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>30.74</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>30.78</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>30.74</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>35143978.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>22291984.6</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>22291984.6</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>23649008.0</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>56869418.44</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>56869418.44</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-162798.7500877455</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>35143978</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>35143978.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>30.07999999999999</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>30.85</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>30.7</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>30.85</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>30.7</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>25196963.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>28414475.0</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>28414475</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>21988355.3</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>60321009.14</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>60321009.14</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-1193175.078426827</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>25196963</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>25196963.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>30.1</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>30.94</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>30.68</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>30.94</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>30.68</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>23835842.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>28874037.6</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>28874037.6</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>20537696.1</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>61681682.72</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>61681682.72</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>-1556776.258967411</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>23835842</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>23835842.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>30.24</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>31.05</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>30.65</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>31.05</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>30.65</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>9521798.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>26588352.0</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>26588352</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>19928659.1</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>62812311.48</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>62812311.48</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>-1874772.971919414</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>9521798</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>9521798.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>30.53</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>31.2</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>30.64</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>30.64</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>17761342.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>26873168.8</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>26873168.8</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>20750992.2</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>62844856.46</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>62844856.46</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>-728450.2414251491</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>17761342</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>17761342.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>30.77999999999999</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>31.29</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>30.64</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>31.29</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>30.64</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>65756430.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>25006031.4</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>25006031.4</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>21753217.0</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>63370945.72</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>63370945.72</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>52361.45361755416</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>65756430</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>65756430.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>30.94</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>31.35</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>30.63</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>31.35</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>30.63</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>27494776.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>15562235.6</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>15562235.6</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>17019879.4</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>62305411.34</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>62305411.34</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>-3976394.17680778</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>27494776</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>27494776.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>30.93</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>31.36</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>30.6</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>31.36</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>30.6</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>12407414.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>12201354.6</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>12201354.6</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>16099056.0</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>62148356.84</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>62148356.84</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>-5490282.356815122</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>12407414</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>12407414.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>30.88</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>31.34</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>30.57</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>31.34</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>30.57</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>10945882.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>13268966.2</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>13268966.2</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>16472569.1</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>62356377.56</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>62356377.56</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>-5840395.172653642</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>10945882</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>10945882.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>21.12</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>21.46</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>22.5</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>21.46</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>22.5</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>671687205.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>626195530.8</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>626195530.8</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>622132821.3</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>733146356.66</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>733146356.66</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>21189677.43851745</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>671687205</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>671687205.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>20.81</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>21.49</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>22.5</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>21.49</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>22.5</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>494560639.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>640193393.2</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>640193393.2</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>603452151.2</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>734438326.0</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>734438326</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>18607123.49500573</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>494560639</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>494560639.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>20.74</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>21.57</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>22.54</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>21.57</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>22.54</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>952963874.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>684968154.0</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>684968154</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>608460649.9</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>745292054.98</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>745292054.98</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>33231066.95088148</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>952963874</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>952963874.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>20.8</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>21.66</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>22.56</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>21.66</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>22.56</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>508895219.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>572334943.8</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>572334943.8</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>541620112.7</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>742408659.92</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>742408659.92</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>3820958.603886724</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>508895219</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>508895219.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>20.99</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>21.78</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>21.78</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>22.6</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>502870717.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>585463875.6</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>585463875.6</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>527086711.6</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>747869455.14</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>747869455.14</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>9248839.765184045</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>502870717</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>502870717.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>21.23</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>22.64</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>22.64</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>741676517.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>618070111.8</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>618070111.8</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>508904183.5</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>743559492.34</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>743559492.34</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>17318122.36113799</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>741676517</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>741676517.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>21.6</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>22.02</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>22.68</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>22.02</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>22.68</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>718434443.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>566710909.2</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>566710909.2</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>472748946.4</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>736966797.76</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>736966797.76</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>2640828.842460155</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>718434443</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>718434443.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>21.83</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>22.14</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>22.71</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>22.14</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>22.71</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>389797823.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>531953145.8</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>531953145.8</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>473420250.2</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>729928690.36</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>729928690.36</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>-15930826.42859614</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>389797823</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>389797823.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>21.91</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>22.24</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>22.72</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>22.24</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>22.72</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>574539878.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>510905281.6</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>510905281.6</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>532030878.4</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>733920278.26</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>733920278.26</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>-6681738.014798105</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>574539878</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>574539878.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>21.96</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>22.31</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>22.74</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>22.31</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>22.74</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>665901898.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>468709547.6</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>468709547.6</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>524403302.2</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>731032785.28</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>731032785.28</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>-13023912.6731295</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>665901898</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>665901898.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>21.88</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>22.36</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>22.75</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>22.36</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>22.75</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>484880504.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>399738255.2</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>399738255.2</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>517022636.4</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>736449789.18</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>736449789.1799999</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>-31407810.30384827</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>484880504</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>484880504.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>

--- a/Result/checksun_type/預拌混凝土.xlsx
+++ b/Result/checksun_type/預拌混凝土.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CJ67"/>
+  <dimension ref="A1:CJ57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19439,11 +19439,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>【b1】</t>
-        </is>
-      </c>
+      <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
           <t>1104</t>
@@ -19451,12 +19447,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1037.682</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -19466,7 +19462,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -19476,52 +19472,52 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>-14.31</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>2025-10-17 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2025-10-30 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -19531,22 +19527,22 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
@@ -19556,27 +19552,27 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>4.80</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr"/>
@@ -19592,131 +19588,131 @@
       </c>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>93.75</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>79.17</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH46" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="AI46" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AL46" t="inlineStr">
         <is>
-          <t>31.66</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM46" t="n">
-        <v>31.07</v>
+        <v>0</v>
       </c>
       <c r="AN46" t="n">
-        <v>31.01</v>
+        <v>0</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>30.42</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>52.24</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ46" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AR46" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="AS46" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr">
         <is>
-          <t>-83.20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>2025/11/25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
-          <t>54922605.53889675</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>33161921.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX46" t="n">
-        <v>20537517.2</v>
+        <v>0</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>23968423.6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AZ46" t="n">
-        <v>30380510.94</v>
+        <v>0</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>-3430906</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
         <is>
-          <t>-1207774.678679961</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BC46" t="inlineStr">
         <is>
-          <t>-639124.9061039723</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BD46" t="inlineStr">
         <is>
-          <t>33161921.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF46" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BG46" t="inlineStr">
         <is>
-          <t>2025/12/02</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BI46" t="inlineStr">
@@ -19761,17 +19757,17 @@
       </c>
       <c r="BQ46" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BR46" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS46" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BT46" t="inlineStr">
@@ -19821,27 +19817,27 @@
       </c>
       <c r="CC46" t="inlineStr">
         <is>
-          <t>水泥工業右上上市</t>
+          <t>水泥工業右下上市</t>
         </is>
       </c>
       <c r="CD46" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE46" t="inlineStr">
         <is>
-          <t>32.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF46" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG46" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CH46" t="inlineStr">
@@ -19863,22 +19859,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1104</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>553.8</t>
+          <t>15342.295</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -19888,7 +19884,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -19898,102 +19894,102 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>-27.81</t>
+          <t>-22.90</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-02-25 00:00:00</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-03-11 00:00:00</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>2025-10-17 00:00:00</t>
+          <t>2024-11-27 00:00:00</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2025-10-30 00:00:00</t>
+          <t>2024-12-09 00:00:00</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>33.4</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>33.55</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-35.20</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>8.10</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
@@ -20004,151 +20000,151 @@
       <c r="AC47" t="inlineStr"/>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>126</t>
         </is>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>1038</t>
+          <t>15342</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>69.35</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AH47" t="n">
-        <v>-0.03</v>
+        <v>-1.01</v>
       </c>
       <c r="AI47" t="n">
-        <v>1.6</v>
+        <v>4.1</v>
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AL47" t="inlineStr">
         <is>
-          <t>31.51</t>
+          <t>22.78</t>
         </is>
       </c>
       <c r="AM47" t="n">
-        <v>31.01</v>
+        <v>21.88</v>
       </c>
       <c r="AN47" t="n">
-        <v>30.97</v>
+        <v>22.47</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>30.35</t>
+          <t>22.65</t>
         </is>
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>55.45</t>
+          <t>1735.46</t>
         </is>
       </c>
       <c r="AQ47" t="n">
-        <v>0.22</v>
+        <v>0.17</v>
       </c>
       <c r="AR47" t="n">
-        <v>0.14</v>
+        <v>-0.01</v>
       </c>
       <c r="AS47" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr">
         <is>
-          <t>-85.39</t>
+          <t>-101.21</t>
         </is>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>2025/11/25</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
-          <t>54922605.53889675</t>
+          <t>991000616.0425532</t>
         </is>
       </c>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>17462561.0</t>
+          <t>348371516.0</t>
         </is>
       </c>
       <c r="AX47" t="n">
-        <v>17446937.6</v>
+        <v>469675041</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>24166629.3</t>
+          <t>609149921.7</t>
         </is>
       </c>
       <c r="AZ47" t="n">
-        <v>30245364.06</v>
+        <v>595644091.12</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
-          <t>-6719691</t>
+          <t>-139474880</t>
         </is>
       </c>
       <c r="BB47" t="inlineStr">
         <is>
-          <t>-1311165.54642105</t>
+          <t>6468947.045829888</t>
         </is>
       </c>
       <c r="BC47" t="inlineStr">
         <is>
-          <t>-1820767.447408877</t>
+          <t>-26436125.46436095</t>
         </is>
       </c>
       <c r="BD47" t="inlineStr">
         <is>
-          <t>17462561.0</t>
+          <t>348371516.0</t>
         </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF47" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="BG47" t="inlineStr">
         <is>
-          <t>2025/12/02</t>
+          <t>2025/10/15</t>
         </is>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="BI47" t="inlineStr">
         <is>
-          <t>環泥</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="BJ47" t="inlineStr">
         <is>
-          <t>環泥</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="BK47" t="inlineStr">
@@ -20163,27 +20159,27 @@
       </c>
       <c r="BM47" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="BN47" t="inlineStr">
         <is>
-          <t>2.214990804444966</t>
+          <t>4.325437847889285</t>
         </is>
       </c>
       <c r="BO47" t="inlineStr">
         <is>
-          <t>12.63883653040306</t>
+          <t>-14.68663446383302</t>
         </is>
       </c>
       <c r="BP47" t="inlineStr">
         <is>
-          <t>-0.1425549787495159</t>
+          <t>1.195709166622471</t>
         </is>
       </c>
       <c r="BQ47" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR47" t="inlineStr">
@@ -20193,32 +20189,32 @@
       </c>
       <c r="BS47" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BT47" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="BU47" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="BV47" t="inlineStr">
         <is>
-          <t>13.57</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW47" t="inlineStr">
         <is>
-          <t>20.60%</t>
+          <t>22.64%</t>
         </is>
       </c>
       <c r="BX47" t="inlineStr">
         <is>
-          <t>13.03%</t>
+          <t>13.16%</t>
         </is>
       </c>
       <c r="BY47" t="inlineStr">
@@ -20228,79 +20224,79 @@
       </c>
       <c r="BZ47" t="inlineStr">
         <is>
-          <t>21905</t>
+          <t>170279</t>
         </is>
       </c>
       <c r="CA47" t="inlineStr">
         <is>
-          <t>預拌混凝土64.00%、水泥22.00%、石膏板14.00% (2024年)</t>
+          <t>水泥,預拌混擬土76.31%、電力供給及儲能,可充式鋰離20.52%、海陸運輸3.17% (2024年)</t>
         </is>
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>環泥-水泥工業-上市</t>
+          <t>台泥-水泥工業-上市</t>
         </is>
       </c>
       <c r="CC47" t="inlineStr">
         <is>
-          <t>水泥工業右上上市</t>
+          <t>水泥工業右下上市</t>
         </is>
       </c>
       <c r="CD47" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>22.7</t>
         </is>
       </c>
       <c r="CE47" t="inlineStr">
         <is>
-          <t>32.1</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CF47" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="CG47" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="CH47" t="inlineStr">
         <is>
-          <t>33.81</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="CI47" t="inlineStr">
         <is>
-          <t>** 水泥 - 水泥成品、預拌混凝土</t>
+          <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
         </is>
       </c>
       <c r="CJ47" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1104</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>681.752</t>
+          <t>22930.834</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -20310,7 +20306,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>22.7</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -20320,257 +20316,257 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>-32.49</t>
+          <t>-15.17</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-02-25 00:00:00</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-03-11 00:00:00</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>2025-10-17 00:00:00</t>
+          <t>2024-11-27 00:00:00</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2025-10-30 00:00:00</t>
+          <t>2024-12-09 00:00:00</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>33.4</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>33.55</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-34.77</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>12.10</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr"/>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>126</t>
         </is>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>1038</t>
+          <t>15342</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>85.71</t>
         </is>
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>77.75</t>
+          <t>95.24</t>
         </is>
       </c>
       <c r="AH48" t="n">
-        <v>1.43</v>
+        <v>-0.57</v>
       </c>
       <c r="AI48" t="n">
-        <v>1.72</v>
+        <v>4.49</v>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AL48" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>22.83</t>
         </is>
       </c>
       <c r="AM48" t="n">
-        <v>30.97</v>
+        <v>21.85</v>
       </c>
       <c r="AN48" t="n">
-        <v>30.94</v>
+        <v>22.49</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>30.29</t>
+          <t>22.68</t>
         </is>
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>82.42</t>
+          <t>397.30</t>
         </is>
       </c>
       <c r="AQ48" t="n">
-        <v>0.22</v>
+        <v>0.17</v>
       </c>
       <c r="AR48" t="n">
-        <v>0.12</v>
+        <v>-0.06</v>
       </c>
       <c r="AS48" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr">
         <is>
-          <t>-87.42</t>
+          <t>-106.47</t>
         </is>
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>2025/11/25</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
-          <t>54922605.53889675</t>
+          <t>991000616.0425532</t>
         </is>
       </c>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>21695428.0</t>
+          <t>518462876.0</t>
         </is>
       </c>
       <c r="AX48" t="n">
-        <v>16836435.2</v>
+        <v>568040850</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
-          <t>24940069.5</t>
+          <t>669609157.5</t>
         </is>
       </c>
       <c r="AZ48" t="n">
-        <v>30222709.22</v>
+        <v>620096910.86</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
-          <t>-8103634</t>
+          <t>-101568307</t>
         </is>
       </c>
       <c r="BB48" t="inlineStr">
         <is>
-          <t>-1218510.655332354</t>
+          <t>12451687.50222822</t>
         </is>
       </c>
       <c r="BC48" t="inlineStr">
         <is>
-          <t>-1761726.526151281</t>
+          <t>-8393825.69001174</t>
         </is>
       </c>
       <c r="BD48" t="inlineStr">
         <is>
-          <t>21695428.0</t>
+          <t>518462876.0</t>
         </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF48" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="BG48" t="inlineStr">
         <is>
-          <t>2025/12/02</t>
+          <t>2025/10/15</t>
         </is>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="BI48" t="inlineStr">
         <is>
-          <t>環泥</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="BJ48" t="inlineStr">
         <is>
-          <t>環泥</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="BK48" t="inlineStr">
@@ -20585,27 +20581,27 @@
       </c>
       <c r="BM48" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="BN48" t="inlineStr">
         <is>
-          <t>2.214990804444966</t>
+          <t>4.325437847889285</t>
         </is>
       </c>
       <c r="BO48" t="inlineStr">
         <is>
-          <t>12.63883653040306</t>
+          <t>-14.68663446383302</t>
         </is>
       </c>
       <c r="BP48" t="inlineStr">
         <is>
-          <t>-0.1425549787495159</t>
+          <t>1.195709166622471</t>
         </is>
       </c>
       <c r="BQ48" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR48" t="inlineStr">
@@ -20615,32 +20611,32 @@
       </c>
       <c r="BS48" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BT48" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="BU48" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="BV48" t="inlineStr">
         <is>
-          <t>13.57</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW48" t="inlineStr">
         <is>
-          <t>20.60%</t>
+          <t>22.64%</t>
         </is>
       </c>
       <c r="BX48" t="inlineStr">
         <is>
-          <t>13.03%</t>
+          <t>13.16%</t>
         </is>
       </c>
       <c r="BY48" t="inlineStr">
@@ -20650,79 +20646,79 @@
       </c>
       <c r="BZ48" t="inlineStr">
         <is>
-          <t>21905</t>
+          <t>170279</t>
         </is>
       </c>
       <c r="CA48" t="inlineStr">
         <is>
-          <t>預拌混凝土64.00%、水泥22.00%、石膏板14.00% (2024年)</t>
+          <t>水泥,預拌混擬土76.31%、電力供給及儲能,可充式鋰離20.52%、海陸運輸3.17% (2024年)</t>
         </is>
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>環泥-水泥工業-上市</t>
+          <t>台泥-水泥工業-上市</t>
         </is>
       </c>
       <c r="CC48" t="inlineStr">
         <is>
-          <t>水泥工業右上上市</t>
+          <t>水泥工業右下上市</t>
         </is>
       </c>
       <c r="CD48" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CE48" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CF48" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CG48" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>22.7</t>
         </is>
       </c>
       <c r="CH48" t="inlineStr">
         <is>
-          <t>33.81</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="CI48" t="inlineStr">
         <is>
-          <t>** 水泥 - 水泥成品、預拌混凝土</t>
+          <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
         </is>
       </c>
       <c r="CJ48" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1104</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>345.228</t>
+          <t>23246.432</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -20732,7 +20728,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>31.45</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -20742,102 +20738,102 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>-39.69</t>
+          <t>5.35</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-02-25 00:00:00</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-03-11 00:00:00</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>2025-10-17 00:00:00</t>
+          <t>2024-11-27 00:00:00</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2025-10-30 00:00:00</t>
+          <t>2024-12-09 00:00:00</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>33.4</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>33.55</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-34.05</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>12.27</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
@@ -20848,151 +20844,151 @@
       <c r="AC49" t="inlineStr"/>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>126</t>
         </is>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>1038</t>
+          <t>15342</t>
         </is>
       </c>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>64.29</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>65.63</t>
+          <t>99.28</t>
         </is>
       </c>
       <c r="AH49" t="n">
-        <v>0.03</v>
+        <v>0.39</v>
       </c>
       <c r="AI49" t="n">
-        <v>1.69</v>
+        <v>4.85</v>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AL49" t="inlineStr">
         <is>
-          <t>31.44</t>
+          <t>22.86</t>
         </is>
       </c>
       <c r="AM49" t="n">
-        <v>30.92</v>
+        <v>21.8</v>
       </c>
       <c r="AN49" t="n">
-        <v>30.89</v>
+        <v>22.53</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>22.7</t>
         </is>
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>81.80</t>
+          <t>227.74</t>
         </is>
       </c>
       <c r="AQ49" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AR49" t="n">
-        <v>0.1</v>
+        <v>-0.11</v>
       </c>
       <c r="AS49" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr">
         <is>
-          <t>-90.01</t>
+          <t>-112.90</t>
         </is>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>2025/11/25</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
-          <t>54922605.53889675</t>
+          <t>991000616.0425532</t>
         </is>
       </c>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>10846856.0</t>
+          <t>537286529.0</t>
         </is>
       </c>
       <c r="AX49" t="n">
-        <v>15171133.2</v>
+        <v>704433174.6</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>25154110.9</t>
+          <t>668652391.8</t>
         </is>
       </c>
       <c r="AZ49" t="n">
-        <v>30546105.2</v>
+        <v>679174314.1799999</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>-9982977</t>
+          <t>35780782</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
         <is>
-          <t>-1119744.133365277</t>
+          <t>16241780.80990822</t>
         </is>
       </c>
       <c r="BC49" t="inlineStr">
         <is>
-          <t>-2067985.012706455</t>
+          <t>-543406.5234410763</t>
         </is>
       </c>
       <c r="BD49" t="inlineStr">
         <is>
-          <t>10846856.0</t>
+          <t>537286529.0</t>
         </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF49" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="BG49" t="inlineStr">
         <is>
-          <t>2025/12/02</t>
+          <t>2025/10/15</t>
         </is>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI49" t="inlineStr">
         <is>
-          <t>環泥</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="BJ49" t="inlineStr">
         <is>
-          <t>環泥</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="BK49" t="inlineStr">
@@ -21007,27 +21003,27 @@
       </c>
       <c r="BM49" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="BN49" t="inlineStr">
         <is>
-          <t>2.214990804444966</t>
+          <t>4.325437847889285</t>
         </is>
       </c>
       <c r="BO49" t="inlineStr">
         <is>
-          <t>12.63883653040306</t>
+          <t>-14.68663446383302</t>
         </is>
       </c>
       <c r="BP49" t="inlineStr">
         <is>
-          <t>-0.1425549787495159</t>
+          <t>1.195709166622471</t>
         </is>
       </c>
       <c r="BQ49" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR49" t="inlineStr">
@@ -21037,32 +21033,32 @@
       </c>
       <c r="BS49" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BT49" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="BU49" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="BV49" t="inlineStr">
         <is>
-          <t>13.57</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW49" t="inlineStr">
         <is>
-          <t>20.60%</t>
+          <t>22.64%</t>
         </is>
       </c>
       <c r="BX49" t="inlineStr">
         <is>
-          <t>13.03%</t>
+          <t>13.16%</t>
         </is>
       </c>
       <c r="BY49" t="inlineStr">
@@ -21072,79 +21068,79 @@
       </c>
       <c r="BZ49" t="inlineStr">
         <is>
-          <t>21905</t>
+          <t>170279</t>
         </is>
       </c>
       <c r="CA49" t="inlineStr">
         <is>
-          <t>預拌混凝土64.00%、水泥22.00%、石膏板14.00% (2024年)</t>
+          <t>水泥,預拌混擬土76.31%、電力供給及儲能,可充式鋰離20.52%、海陸運輸3.17% (2024年)</t>
         </is>
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>環泥-水泥工業-上市</t>
+          <t>台泥-水泥工業-上市</t>
         </is>
       </c>
       <c r="CC49" t="inlineStr">
         <is>
-          <t>水泥工業右上上市</t>
+          <t>水泥工業右下上市</t>
         </is>
       </c>
       <c r="CD49" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CE49" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="CF49" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CG49" t="inlineStr">
         <is>
-          <t>31.45</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CH49" t="inlineStr">
         <is>
-          <t>33.81</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="CI49" t="inlineStr">
         <is>
-          <t>** 水泥 - 水泥成品、預拌混凝土</t>
+          <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
         </is>
       </c>
       <c r="CJ49" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1104</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>621.676</t>
+          <t>18924.305</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -21154,7 +21150,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -21164,102 +21160,102 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>-3.41</t>
+          <t>5.87</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-02-25 00:00:00</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-03-11 00:00:00</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>2025-10-17 00:00:00</t>
+          <t>2024-11-27 00:00:00</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2025-10-30 00:00:00</t>
+          <t>2024-12-09 00:00:00</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>33.4</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>33.55</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-34.20</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
@@ -21270,151 +21266,151 @@
       <c r="AC50" t="inlineStr"/>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>126</t>
         </is>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>1038</t>
+          <t>15342</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>68.97</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>70.13</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="AH50" t="n">
-        <v>-0.13</v>
+        <v>0.93</v>
       </c>
       <c r="AI50" t="n">
-        <v>2.19</v>
+        <v>4.42</v>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AL50" t="inlineStr">
         <is>
-          <t>31.54</t>
+          <t>22.69</t>
         </is>
       </c>
       <c r="AM50" t="n">
-        <v>30.86</v>
+        <v>21.73</v>
       </c>
       <c r="AN50" t="n">
-        <v>30.86</v>
+        <v>22.54</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>30.17</t>
+          <t>22.72</t>
         </is>
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>114.96</t>
+          <t>148.50</t>
         </is>
       </c>
       <c r="AQ50" t="n">
-        <v>0.16</v>
+        <v>0.09</v>
       </c>
       <c r="AR50" t="n">
-        <v>0.08</v>
+        <v>-0.18</v>
       </c>
       <c r="AS50" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr">
         <is>
-          <t>-92.05</t>
+          <t>-120.25</t>
         </is>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>2025/11/25</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
-          <t>54922605.53889675</t>
+          <t>991000616.0425532</t>
         </is>
       </c>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>19520820.0</t>
+          <t>432691470.0</t>
         </is>
       </c>
       <c r="AX50" t="n">
-        <v>24167478</v>
+        <v>704226090.4</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>25021605.1</t>
+          <t>665210810.6</t>
         </is>
       </c>
       <c r="AZ50" t="n">
-        <v>30996679.94</v>
+        <v>756181820.36</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>-854127</t>
+          <t>39015279</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
         <is>
-          <t>-947336.70075779</t>
+          <t>19293633.05233536</t>
         </is>
       </c>
       <c r="BC50" t="inlineStr">
         <is>
-          <t>-1269293.528760046</t>
+          <t>8674065.41178286</t>
         </is>
       </c>
       <c r="BD50" t="inlineStr">
         <is>
-          <t>19520820.0</t>
+          <t>432691470.0</t>
         </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF50" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="BG50" t="inlineStr">
         <is>
-          <t>2025/12/02</t>
+          <t>2025/10/15</t>
         </is>
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="BI50" t="inlineStr">
         <is>
-          <t>環泥</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="BJ50" t="inlineStr">
         <is>
-          <t>環泥</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="BK50" t="inlineStr">
@@ -21429,62 +21425,62 @@
       </c>
       <c r="BM50" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="BN50" t="inlineStr">
         <is>
-          <t>2.214990804444966</t>
+          <t>4.325437847889285</t>
         </is>
       </c>
       <c r="BO50" t="inlineStr">
         <is>
-          <t>12.63883653040306</t>
+          <t>-14.68663446383302</t>
         </is>
       </c>
       <c r="BP50" t="inlineStr">
         <is>
-          <t>-0.1425549787495159</t>
+          <t>1.195709166622471</t>
         </is>
       </c>
       <c r="BQ50" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR50" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS50" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BT50" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="BU50" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="BV50" t="inlineStr">
         <is>
-          <t>13.57</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW50" t="inlineStr">
         <is>
-          <t>20.60%</t>
+          <t>22.64%</t>
         </is>
       </c>
       <c r="BX50" t="inlineStr">
         <is>
-          <t>13.03%</t>
+          <t>13.16%</t>
         </is>
       </c>
       <c r="BY50" t="inlineStr">
@@ -21494,57 +21490,57 @@
       </c>
       <c r="BZ50" t="inlineStr">
         <is>
-          <t>21905</t>
+          <t>170279</t>
         </is>
       </c>
       <c r="CA50" t="inlineStr">
         <is>
-          <t>預拌混凝土64.00%、水泥22.00%、石膏板14.00% (2024年)</t>
+          <t>水泥,預拌混擬土76.31%、電力供給及儲能,可充式鋰離20.52%、海陸運輸3.17% (2024年)</t>
         </is>
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>環泥-水泥工業-上市</t>
+          <t>台泥-水泥工業-上市</t>
         </is>
       </c>
       <c r="CC50" t="inlineStr">
         <is>
-          <t>水泥工業右上上市</t>
+          <t>水泥工業右下上市</t>
         </is>
       </c>
       <c r="CD50" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CE50" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="CF50" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>22.65</t>
         </is>
       </c>
       <c r="CG50" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CH50" t="inlineStr">
         <is>
-          <t>33.81</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="CI50" t="inlineStr">
         <is>
-          <t>** 水泥 - 水泥成品、預拌混凝土</t>
+          <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
         </is>
       </c>
       <c r="CJ50" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -21556,17 +21552,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1104</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>566.107</t>
+          <t>22416.9</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -21576,7 +21572,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>31.15</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -21586,102 +21582,102 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>10.28</t>
+          <t>8.03</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-02-25 00:00:00</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-03-11 00:00:00</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>2025-10-17 00:00:00</t>
+          <t>2024-11-27 00:00:00</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2025-10-30 00:00:00</t>
+          <t>2024-12-09 00:00:00</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>33.4</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>33.55</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-34.48</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>11.83</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
@@ -21692,151 +21688,151 @@
       <c r="AC51" t="inlineStr"/>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>126</t>
         </is>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
-          <t>1038</t>
+          <t>15342</t>
         </is>
       </c>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>63.64</t>
+          <t>97.83</t>
         </is>
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>76.03</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="AH51" t="n">
-        <v>-1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AI51" t="n">
-        <v>2.37</v>
+        <v>3.97</v>
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AL51" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="AM51" t="n">
-        <v>30.82</v>
+        <v>21.64</v>
       </c>
       <c r="AN51" t="n">
-        <v>30.83</v>
+        <v>22.52</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>30.11</t>
+          <t>22.74</t>
         </is>
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>163.61</t>
+          <t>106.33</t>
         </is>
       </c>
       <c r="AQ51" t="n">
-        <v>0.14</v>
+        <v>0.02</v>
       </c>
       <c r="AR51" t="n">
-        <v>0.05</v>
+        <v>-0.24</v>
       </c>
       <c r="AS51" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr">
         <is>
-          <t>-94.34</t>
+          <t>-127.77</t>
         </is>
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>2025/11/25</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
-          <t>54922605.53889675</t>
+          <t>991000616.0425532</t>
         </is>
       </c>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>17709023.0</t>
+          <t>511562814.0</t>
         </is>
       </c>
       <c r="AX51" t="n">
-        <v>27399330</v>
+        <v>752025237.4</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
-          <t>24845657.3</t>
+          <t>696109315.3</t>
         </is>
       </c>
       <c r="AZ51" t="n">
-        <v>31211481.62</v>
+        <v>757139109.14</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
-          <t>2553672</t>
+          <t>55915922</t>
         </is>
       </c>
       <c r="BB51" t="inlineStr">
         <is>
-          <t>-888799.0956664707</t>
+          <t>21224463.53243582</t>
         </is>
       </c>
       <c r="BC51" t="inlineStr">
         <is>
-          <t>-1012327.068523746</t>
+          <t>32738707.87596762</t>
         </is>
       </c>
       <c r="BD51" t="inlineStr">
         <is>
-          <t>17709023.0</t>
+          <t>511562814.0</t>
         </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF51" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="BG51" t="inlineStr">
         <is>
-          <t>2025/12/02</t>
+          <t>2025/10/15</t>
         </is>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="BI51" t="inlineStr">
         <is>
-          <t>環泥</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="BJ51" t="inlineStr">
         <is>
-          <t>環泥</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="BK51" t="inlineStr">
@@ -21851,27 +21847,27 @@
       </c>
       <c r="BM51" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="BN51" t="inlineStr">
         <is>
-          <t>2.214990804444966</t>
+          <t>4.325437847889285</t>
         </is>
       </c>
       <c r="BO51" t="inlineStr">
         <is>
-          <t>12.63883653040306</t>
+          <t>-14.68663446383302</t>
         </is>
       </c>
       <c r="BP51" t="inlineStr">
         <is>
-          <t>-0.1425549787495159</t>
+          <t>1.195709166622471</t>
         </is>
       </c>
       <c r="BQ51" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR51" t="inlineStr">
@@ -21881,32 +21877,32 @@
       </c>
       <c r="BS51" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BT51" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="BU51" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="BV51" t="inlineStr">
         <is>
-          <t>13.57</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW51" t="inlineStr">
         <is>
-          <t>20.60%</t>
+          <t>22.64%</t>
         </is>
       </c>
       <c r="BX51" t="inlineStr">
         <is>
-          <t>13.03%</t>
+          <t>13.16%</t>
         </is>
       </c>
       <c r="BY51" t="inlineStr">
@@ -21916,79 +21912,79 @@
       </c>
       <c r="BZ51" t="inlineStr">
         <is>
-          <t>21905</t>
+          <t>170279</t>
         </is>
       </c>
       <c r="CA51" t="inlineStr">
         <is>
-          <t>預拌混凝土64.00%、水泥22.00%、石膏板14.00% (2024年)</t>
+          <t>水泥,預拌混擬土76.31%、電力供給及儲能,可充式鋰離20.52%、海陸運輸3.17% (2024年)</t>
         </is>
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>環泥-水泥工業-上市</t>
+          <t>台泥-水泥工業-上市</t>
         </is>
       </c>
       <c r="CC51" t="inlineStr">
         <is>
-          <t>水泥工業右上上市</t>
+          <t>水泥工業右下上市</t>
         </is>
       </c>
       <c r="CD51" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CE51" t="inlineStr">
         <is>
-          <t>31.45</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CF51" t="inlineStr">
         <is>
-          <t>31.15</t>
+          <t>22.7</t>
         </is>
       </c>
       <c r="CG51" t="inlineStr">
         <is>
-          <t>31.15</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="CH51" t="inlineStr">
         <is>
-          <t>33.81</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="CI51" t="inlineStr">
         <is>
-          <t>** 水泥 - 水泥成品、預拌混凝土</t>
+          <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
         </is>
       </c>
       <c r="CJ51" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1104</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>456.882</t>
+          <t>36403.182</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -21998,7 +21994,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>31.45</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -22008,257 +22004,257 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
+          <t>4.44</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>-99.0</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2025-02-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>2025-03-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>2024-11-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>2024-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>34.95</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>34.8</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>33.4</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>33.55</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>-34.48</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
           <t>4.17</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>2025-12-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>2025-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>2025-10-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>31.95</t>
-        </is>
-      </c>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>31.95</t>
-        </is>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>31.1</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>31.3</t>
-        </is>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>-1.56</t>
-        </is>
-      </c>
-      <c r="W52" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>2.08</t>
-        </is>
-      </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>19.21</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr"/>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>126</t>
         </is>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>1038</t>
+          <t>15342</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>97.96</t>
         </is>
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>88.15</t>
+          <t>99.32</t>
         </is>
       </c>
       <c r="AH52" t="n">
-        <v>-0.22</v>
+        <v>2.8</v>
       </c>
       <c r="AI52" t="n">
-        <v>2.25</v>
+        <v>2.9</v>
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AL52" t="inlineStr">
         <is>
-          <t>31.52</t>
+          <t>22.18</t>
         </is>
       </c>
       <c r="AM52" t="n">
-        <v>30.82</v>
+        <v>21.56</v>
       </c>
       <c r="AN52" t="n">
-        <v>30.8</v>
+        <v>22.51</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>30.06</t>
+          <t>22.76</t>
         </is>
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>368.26</t>
+          <t>78.93</t>
         </is>
       </c>
       <c r="AQ52" t="n">
-        <v>0.15</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AR52" t="n">
-        <v>0.03</v>
+        <v>-0.31</v>
       </c>
       <c r="AS52" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr">
         <is>
-          <t>-96.65</t>
+          <t>-135.15</t>
         </is>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>2025/11/25</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
-          <t>54922605.53889675</t>
+          <t>991000616.0425532</t>
         </is>
       </c>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>14410049.0</t>
+          <t>840200561.0</t>
         </is>
       </c>
       <c r="AX52" t="n">
-        <v>30886321</v>
+        <v>748624802.4</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>29650398.0</t>
+          <t>716796478.2</t>
         </is>
       </c>
       <c r="AZ52" t="n">
-        <v>31860520.44</v>
+        <v>757710850.26</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>1235923</t>
+          <t>31828324</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
         <is>
-          <t>-866339.4642378751</t>
+          <t>19130964.56088458</t>
         </is>
       </c>
       <c r="BC52" t="inlineStr">
         <is>
-          <t>-414956.4800246134</t>
+          <t>57497027.82923281</t>
         </is>
       </c>
       <c r="BD52" t="inlineStr">
         <is>
-          <t>14410049.0</t>
+          <t>840200561.0</t>
         </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF52" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="BG52" t="inlineStr">
         <is>
-          <t>2025/12/02</t>
+          <t>2025/10/15</t>
         </is>
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="BI52" t="inlineStr">
         <is>
-          <t>環泥</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="BJ52" t="inlineStr">
         <is>
-          <t>環泥</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="BK52" t="inlineStr">
@@ -22273,62 +22269,62 @@
       </c>
       <c r="BM52" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="BN52" t="inlineStr">
         <is>
-          <t>2.214990804444966</t>
+          <t>4.325437847889285</t>
         </is>
       </c>
       <c r="BO52" t="inlineStr">
         <is>
-          <t>12.63883653040306</t>
+          <t>-14.68663446383302</t>
         </is>
       </c>
       <c r="BP52" t="inlineStr">
         <is>
-          <t>-0.1425549787495159</t>
+          <t>1.195709166622471</t>
         </is>
       </c>
       <c r="BQ52" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR52" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS52" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BT52" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="BU52" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="BV52" t="inlineStr">
         <is>
-          <t>13.57</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW52" t="inlineStr">
         <is>
-          <t>20.60%</t>
+          <t>22.64%</t>
         </is>
       </c>
       <c r="BX52" t="inlineStr">
         <is>
-          <t>13.03%</t>
+          <t>13.16%</t>
         </is>
       </c>
       <c r="BY52" t="inlineStr">
@@ -22338,79 +22334,79 @@
       </c>
       <c r="BZ52" t="inlineStr">
         <is>
-          <t>21905</t>
+          <t>170279</t>
         </is>
       </c>
       <c r="CA52" t="inlineStr">
         <is>
-          <t>預拌混凝土64.00%、水泥22.00%、石膏板14.00% (2024年)</t>
+          <t>水泥,預拌混擬土76.31%、電力供給及儲能,可充式鋰離20.52%、海陸運輸3.17% (2024年)</t>
         </is>
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>環泥-水泥工業-上市</t>
+          <t>台泥-水泥工業-上市</t>
         </is>
       </c>
       <c r="CC52" t="inlineStr">
         <is>
-          <t>水泥工業右上上市</t>
+          <t>水泥工業右下上市</t>
         </is>
       </c>
       <c r="CD52" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CE52" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>23.45</t>
         </is>
       </c>
       <c r="CF52" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="CG52" t="inlineStr">
         <is>
-          <t>31.45</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="CH52" t="inlineStr">
         <is>
-          <t>33.81</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="CI52" t="inlineStr">
         <is>
-          <t>** 水泥 - 水泥成品、預拌混凝土</t>
+          <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
         </is>
       </c>
       <c r="CJ52" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1104</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>420.864</t>
+          <t>52859.34</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -22420,7 +22416,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -22430,257 +22426,257 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>6.73</t>
+          <t>14.80</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-02-25 00:00:00</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-03-11 00:00:00</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>2025-10-17 00:00:00</t>
+          <t>2024-11-27 00:00:00</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2025-10-30 00:00:00</t>
+          <t>2024-12-09 00:00:00</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>33.4</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>33.55</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-34.34</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>27.90</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr"/>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>126</t>
         </is>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>1038</t>
+          <t>15342</t>
         </is>
       </c>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>86.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>95.56</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH53" t="n">
-        <v>0.99</v>
+        <v>4.53</v>
       </c>
       <c r="AI53" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-4.5</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AL53" t="inlineStr">
         <is>
-          <t>31.34</t>
+          <t>21.86</t>
         </is>
       </c>
       <c r="AM53" t="n">
-        <v>30.8</v>
+        <v>21.49</v>
       </c>
       <c r="AN53" t="n">
-        <v>30.77</v>
+        <v>22.5</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>22.78</t>
         </is>
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>4873.90</t>
+          <t>54.87</t>
         </is>
       </c>
       <c r="AQ53" t="n">
-        <v>0.13</v>
+        <v>-0.17</v>
       </c>
       <c r="AR53" t="n">
-        <v>0</v>
+        <v>-0.37</v>
       </c>
       <c r="AS53" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr">
         <is>
-          <t>-99.73</t>
+          <t>-142.09</t>
         </is>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>2025/11/25</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
-          <t>54922605.53889675</t>
+          <t>991000616.0425532</t>
         </is>
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>13368918.0</t>
+          <t>1200424499.0</t>
         </is>
       </c>
       <c r="AX53" t="n">
-        <v>33043703.8</v>
+        <v>771177465</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>30958870.7</t>
+          <t>671756204.4</t>
         </is>
       </c>
       <c r="AZ53" t="n">
-        <v>32906803.2</v>
+        <v>746928524.46</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>2084833</t>
+          <t>99421260</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
         <is>
-          <t>-948409.0977311954</t>
+          <t>12155316.69391218</t>
         </is>
       </c>
       <c r="BC53" t="inlineStr">
         <is>
-          <t>806711.4492607452</t>
+          <t>55601403.87571049</t>
         </is>
       </c>
       <c r="BD53" t="inlineStr">
         <is>
-          <t>13368918.0</t>
+          <t>1200424499.0</t>
         </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF53" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="BG53" t="inlineStr">
         <is>
-          <t>2025/12/02</t>
+          <t>2025/10/15</t>
         </is>
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="BI53" t="inlineStr">
         <is>
-          <t>環泥</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="BJ53" t="inlineStr">
         <is>
-          <t>環泥</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="BK53" t="inlineStr">
@@ -22695,62 +22691,62 @@
       </c>
       <c r="BM53" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="BN53" t="inlineStr">
         <is>
-          <t>2.214990804444966</t>
+          <t>4.325437847889285</t>
         </is>
       </c>
       <c r="BO53" t="inlineStr">
         <is>
-          <t>12.63883653040306</t>
+          <t>-14.68663446383302</t>
         </is>
       </c>
       <c r="BP53" t="inlineStr">
         <is>
-          <t>-0.1425549787495159</t>
+          <t>1.195709166622471</t>
         </is>
       </c>
       <c r="BQ53" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR53" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS53" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BT53" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="BU53" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="BV53" t="inlineStr">
         <is>
-          <t>13.57</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW53" t="inlineStr">
         <is>
-          <t>20.60%</t>
+          <t>22.64%</t>
         </is>
       </c>
       <c r="BX53" t="inlineStr">
         <is>
-          <t>13.03%</t>
+          <t>13.16%</t>
         </is>
       </c>
       <c r="BY53" t="inlineStr">
@@ -22760,79 +22756,79 @@
       </c>
       <c r="BZ53" t="inlineStr">
         <is>
-          <t>21905</t>
+          <t>170279</t>
         </is>
       </c>
       <c r="CA53" t="inlineStr">
         <is>
-          <t>預拌混凝土64.00%、水泥22.00%、石膏板14.00% (2024年)</t>
+          <t>水泥,預拌混擬土76.31%、電力供給及儲能,可充式鋰離20.52%、海陸運輸3.17% (2024年)</t>
         </is>
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>環泥-水泥工業-上市</t>
+          <t>台泥-水泥工業-上市</t>
         </is>
       </c>
       <c r="CC53" t="inlineStr">
         <is>
-          <t>水泥工業右上上市</t>
+          <t>水泥工業右下上市</t>
         </is>
       </c>
       <c r="CD53" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="CE53" t="inlineStr">
         <is>
-          <t>32.05</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CF53" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="CG53" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CH53" t="inlineStr">
         <is>
-          <t>33.81</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="CI53" t="inlineStr">
         <is>
-          <t>** 水泥 - 水泥成品、預拌混凝土</t>
+          <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
         </is>
       </c>
       <c r="CJ53" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1104</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1752.11</t>
+          <t>24336.287</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -22842,7 +22838,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -22852,118 +22848,118 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>13.85</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-02-25 00:00:00</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-03-11 00:00:00</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>2025-10-17 00:00:00</t>
+          <t>2024-11-27 00:00:00</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2025-10-30 00:00:00</t>
+          <t>2024-12-09 00:00:00</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>33.4</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>33.55</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-36.49</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>8.11</t>
+          <t>12.84</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr"/>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>126</t>
         </is>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
-          <t>1038</t>
+          <t>15342</t>
         </is>
       </c>
       <c r="AF54" t="inlineStr">
@@ -22973,136 +22969,136 @@
       </c>
       <c r="AG54" t="inlineStr">
         <is>
-          <t>95.56</t>
+          <t>84.44</t>
         </is>
       </c>
       <c r="AH54" t="n">
-        <v>2.7</v>
+        <v>3.27</v>
       </c>
       <c r="AI54" t="n">
-        <v>1.06</v>
+        <v>-0.24</v>
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-4.62</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AL54" t="inlineStr">
         <is>
-          <t>31.11</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="AM54" t="n">
-        <v>30.78</v>
+        <v>21.45</v>
       </c>
       <c r="AN54" t="n">
-        <v>30.76</v>
+        <v>22.49</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>29.94</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>361.15</t>
+          <t>28.78</t>
         </is>
       </c>
       <c r="AQ54" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="AR54" t="n">
-        <v>-0.03</v>
+        <v>-0.42</v>
       </c>
       <c r="AS54" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr">
         <is>
-          <t>-102.97</t>
+          <t>-147.86</t>
         </is>
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>2025/11/25</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
-          <t>54922605.53889675</t>
+          <t>991000616.0425532</t>
         </is>
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>55828580.0</t>
+          <t>536251108.0</t>
         </is>
       </c>
       <c r="AX54" t="n">
-        <v>35137088.6</v>
+        <v>632871609</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t>30862720.3</t>
+          <t>609167742.3</t>
         </is>
       </c>
       <c r="AZ54" t="n">
-        <v>38981141.32</v>
+        <v>731439820.52</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>4274368</t>
+          <t>23703866</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
         <is>
-          <t>-1267521.924457003</t>
+          <t>4256028.115403395</t>
         </is>
       </c>
       <c r="BC54" t="inlineStr">
         <is>
-          <t>2634689.975051943</t>
+          <t>12312183.30368912</t>
         </is>
       </c>
       <c r="BD54" t="inlineStr">
         <is>
-          <t>55828580.0</t>
+          <t>536251108.0</t>
         </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF54" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="BG54" t="inlineStr">
         <is>
-          <t>2025/12/02</t>
+          <t>2025/10/15</t>
         </is>
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="BI54" t="inlineStr">
         <is>
-          <t>環泥</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="BJ54" t="inlineStr">
         <is>
-          <t>環泥</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="BK54" t="inlineStr">
@@ -23117,62 +23113,62 @@
       </c>
       <c r="BM54" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="BN54" t="inlineStr">
         <is>
-          <t>2.214990804444966</t>
+          <t>4.325437847889285</t>
         </is>
       </c>
       <c r="BO54" t="inlineStr">
         <is>
-          <t>12.63883653040306</t>
+          <t>-14.68663446383302</t>
         </is>
       </c>
       <c r="BP54" t="inlineStr">
         <is>
-          <t>-0.1425549787495159</t>
+          <t>1.195709166622471</t>
         </is>
       </c>
       <c r="BQ54" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR54" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS54" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BT54" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="BU54" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="BV54" t="inlineStr">
         <is>
-          <t>13.57</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW54" t="inlineStr">
         <is>
-          <t>20.60%</t>
+          <t>22.64%</t>
         </is>
       </c>
       <c r="BX54" t="inlineStr">
         <is>
-          <t>13.03%</t>
+          <t>13.16%</t>
         </is>
       </c>
       <c r="BY54" t="inlineStr">
@@ -23182,79 +23178,79 @@
       </c>
       <c r="BZ54" t="inlineStr">
         <is>
-          <t>21905</t>
+          <t>170279</t>
         </is>
       </c>
       <c r="CA54" t="inlineStr">
         <is>
-          <t>預拌混凝土64.00%、水泥22.00%、石膏板14.00% (2024年)</t>
+          <t>水泥,預拌混擬土76.31%、電力供給及儲能,可充式鋰離20.52%、海陸運輸3.17% (2024年)</t>
         </is>
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>環泥-水泥工業-上市</t>
+          <t>台泥-水泥工業-上市</t>
         </is>
       </c>
       <c r="CC54" t="inlineStr">
         <is>
-          <t>水泥工業右上上市</t>
+          <t>水泥工業右下上市</t>
         </is>
       </c>
       <c r="CD54" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="CE54" t="inlineStr">
         <is>
-          <t>32.05</t>
+          <t>22.15</t>
         </is>
       </c>
       <c r="CF54" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="CG54" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="CH54" t="inlineStr">
         <is>
-          <t>33.81</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="CI54" t="inlineStr">
         <is>
-          <t>** 水泥 - 水泥成品、預拌混凝土</t>
+          <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
         </is>
       </c>
       <c r="CJ54" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>【b2】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1104</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1129.25</t>
+          <t>30791.526</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -23264,7 +23260,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -23274,17 +23270,17 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -23294,37 +23290,37 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-02-25 00:00:00</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-03-11 00:00:00</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>2025-10-17 00:00:00</t>
+          <t>2024-11-27 00:00:00</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2025-10-30 00:00:00</t>
+          <t>2024-12-09 00:00:00</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -23334,12 +23330,12 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>33.4</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>33.55</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -23349,27 +23345,27 @@
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-36.93</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>5.22</t>
+          <t>16.25</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
@@ -23380,12 +23376,12 @@
       <c r="AC55" t="inlineStr"/>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>126</t>
         </is>
       </c>
       <c r="AE55" t="inlineStr">
         <is>
-          <t>1038</t>
+          <t>15342</t>
         </is>
       </c>
       <c r="AF55" t="inlineStr">
@@ -23395,106 +23391,106 @@
       </c>
       <c r="AG55" t="inlineStr">
         <is>
-          <t>81.11</t>
+          <t>65.53</t>
         </is>
       </c>
       <c r="AH55" t="n">
-        <v>2.87</v>
+        <v>3.93</v>
       </c>
       <c r="AI55" t="n">
-        <v>-0.31</v>
+        <v>-1.6</v>
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-4.6</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AL55" t="inlineStr">
         <is>
-          <t>30.67</t>
+          <t>21.12</t>
         </is>
       </c>
       <c r="AM55" t="n">
-        <v>30.76</v>
+        <v>21.46</v>
       </c>
       <c r="AN55" t="n">
-        <v>30.73</v>
+        <v>22.5</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>29.87</t>
+          <t>22.82</t>
         </is>
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>55.86</t>
+          <t>13.90</t>
         </is>
       </c>
       <c r="AQ55" t="n">
-        <v>-0.02</v>
+        <v>-0.39</v>
       </c>
       <c r="AR55" t="n">
-        <v>-0.05</v>
+        <v>-0.45</v>
       </c>
       <c r="AS55" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr">
         <is>
-          <t>-105.65</t>
+          <t>-151.31</t>
         </is>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>2025/11/25</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>54922605.53889675</t>
+          <t>991000616.0425532</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>35680080.0</t>
+          <t>671687205.0</t>
         </is>
       </c>
       <c r="AX55" t="n">
-        <v>25875732.2</v>
+        <v>626195530.8</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>26374450.5</t>
+          <t>622132821.3</t>
         </is>
       </c>
       <c r="AZ55" t="n">
-        <v>43918565.22</v>
+        <v>733146356.66</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>-498718</t>
+          <t>4062709</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
         <is>
-          <t>-1977014.997094993</t>
+          <t>2791272.626624172</t>
         </is>
       </c>
       <c r="BC55" t="inlineStr">
         <is>
-          <t>602742.2985018045</t>
+          <t>21192153.54709804</t>
         </is>
       </c>
       <c r="BD55" t="inlineStr">
         <is>
-          <t>35680080.0</t>
+          <t>671687205.0</t>
         </is>
       </c>
       <c r="BE55" t="inlineStr">
@@ -23504,27 +23500,27 @@
       </c>
       <c r="BF55" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="BG55" t="inlineStr">
         <is>
-          <t>2025/12/02</t>
+          <t>2025/10/15</t>
         </is>
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-4.36</t>
         </is>
       </c>
       <c r="BI55" t="inlineStr">
         <is>
-          <t>環泥</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="BJ55" t="inlineStr">
         <is>
-          <t>環泥</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="BK55" t="inlineStr">
@@ -23539,62 +23535,62 @@
       </c>
       <c r="BM55" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="BN55" t="inlineStr">
         <is>
-          <t>2.214990804444966</t>
+          <t>4.325437847889285</t>
         </is>
       </c>
       <c r="BO55" t="inlineStr">
         <is>
-          <t>12.63883653040306</t>
+          <t>-14.68663446383302</t>
         </is>
       </c>
       <c r="BP55" t="inlineStr">
         <is>
-          <t>-0.1425549787495159</t>
+          <t>1.195709166622471</t>
         </is>
       </c>
       <c r="BQ55" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR55" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS55" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BT55" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="BU55" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="BV55" t="inlineStr">
         <is>
-          <t>13.57</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW55" t="inlineStr">
         <is>
-          <t>20.60%</t>
+          <t>22.64%</t>
         </is>
       </c>
       <c r="BX55" t="inlineStr">
         <is>
-          <t>13.03%</t>
+          <t>13.16%</t>
         </is>
       </c>
       <c r="BY55" t="inlineStr">
@@ -23604,79 +23600,79 @@
       </c>
       <c r="BZ55" t="inlineStr">
         <is>
-          <t>21905</t>
+          <t>170279</t>
         </is>
       </c>
       <c r="CA55" t="inlineStr">
         <is>
-          <t>預拌混凝土64.00%、水泥22.00%、石膏板14.00% (2024年)</t>
+          <t>水泥,預拌混擬土76.31%、電力供給及儲能,可充式鋰離20.52%、海陸運輸3.17% (2024年)</t>
         </is>
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>環泥-水泥工業-上市</t>
+          <t>台泥-水泥工業-上市</t>
         </is>
       </c>
       <c r="CC55" t="inlineStr">
         <is>
-          <t>水泥工業右上上市</t>
+          <t>水泥工業右下上市</t>
         </is>
       </c>
       <c r="CD55" t="inlineStr">
         <is>
-          <t>31.2</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CE55" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>22.05</t>
         </is>
       </c>
       <c r="CF55" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CG55" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="CH55" t="inlineStr">
         <is>
-          <t>33.81</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="CI55" t="inlineStr">
         <is>
-          <t>** 水泥 - 水泥成品、預拌混凝土</t>
+          <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
         </is>
       </c>
       <c r="CJ55" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1104</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>1132.45</t>
+          <t>23375.276</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -23686,7 +23682,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -23696,17 +23692,17 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>-5.74</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -23716,37 +23712,37 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-02-25 00:00:00</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-03-11 00:00:00</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>2025-10-17 00:00:00</t>
+          <t>2024-11-27 00:00:00</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>2025-10-30 00:00:00</t>
+          <t>2024-12-09 00:00:00</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -23756,12 +23752,12 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>33.4</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>33.55</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -23771,27 +23767,27 @@
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-39.08</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>12.34</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
@@ -23802,121 +23798,121 @@
       <c r="AC56" t="inlineStr"/>
       <c r="AD56" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>126</t>
         </is>
       </c>
       <c r="AE56" t="inlineStr">
         <is>
-          <t>1038</t>
+          <t>15342</t>
         </is>
       </c>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>86.67</t>
+          <t>53.33</t>
         </is>
       </c>
       <c r="AG56" t="inlineStr">
         <is>
-          <t>65.56</t>
+          <t>34.89</t>
         </is>
       </c>
       <c r="AH56" t="n">
-        <v>2.31</v>
+        <v>1.87</v>
       </c>
       <c r="AI56" t="n">
-        <v>-1.58</v>
+        <v>-3.18</v>
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AL56" t="inlineStr">
         <is>
-          <t>30.3</t>
+          <t>20.81</t>
         </is>
       </c>
       <c r="AM56" t="n">
-        <v>30.78</v>
+        <v>21.49</v>
       </c>
       <c r="AN56" t="n">
-        <v>30.74</v>
+        <v>22.5</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>29.82</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>-75.48</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="AQ56" t="n">
-        <v>-0.11</v>
+        <v>-0.48</v>
       </c>
       <c r="AR56" t="n">
-        <v>-0.06</v>
+        <v>-0.47</v>
       </c>
       <c r="AS56" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr">
         <is>
-          <t>-106.44</t>
+          <t>-153.09</t>
         </is>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>2025/11/25</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
-          <t>54922605.53889675</t>
+          <t>991000616.0425532</t>
         </is>
       </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>35143978.0</t>
+          <t>494560639.0</t>
         </is>
       </c>
       <c r="AX56" t="n">
-        <v>22291984.6</v>
+        <v>640193393.2</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>23649008.0</t>
+          <t>603452151.2</t>
         </is>
       </c>
       <c r="AZ56" t="n">
-        <v>56869418.44</v>
+        <v>734438326</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>-1357023</t>
+          <t>36741242</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
         <is>
-          <t>-2446061.778112593</t>
+          <t>-554342.0861892588</t>
         </is>
       </c>
       <c r="BC56" t="inlineStr">
         <is>
-          <t>-162798.7500877455</t>
+          <t>18609952.30385745</t>
         </is>
       </c>
       <c r="BD56" t="inlineStr">
         <is>
-          <t>35143978.0</t>
+          <t>494560639.0</t>
         </is>
       </c>
       <c r="BE56" t="inlineStr">
@@ -23926,27 +23922,27 @@
       </c>
       <c r="BF56" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="BG56" t="inlineStr">
         <is>
-          <t>2025/12/02</t>
+          <t>2025/10/15</t>
         </is>
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-7.63</t>
         </is>
       </c>
       <c r="BI56" t="inlineStr">
         <is>
-          <t>環泥</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="BJ56" t="inlineStr">
         <is>
-          <t>環泥</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="BK56" t="inlineStr">
@@ -23961,27 +23957,27 @@
       </c>
       <c r="BM56" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="BN56" t="inlineStr">
         <is>
-          <t>2.214990804444966</t>
+          <t>4.325437847889285</t>
         </is>
       </c>
       <c r="BO56" t="inlineStr">
         <is>
-          <t>12.63883653040306</t>
+          <t>-14.68663446383302</t>
         </is>
       </c>
       <c r="BP56" t="inlineStr">
         <is>
-          <t>-0.1425549787495159</t>
+          <t>1.195709166622471</t>
         </is>
       </c>
       <c r="BQ56" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR56" t="inlineStr">
@@ -23991,32 +23987,32 @@
       </c>
       <c r="BS56" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BT56" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="BU56" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="BV56" t="inlineStr">
         <is>
-          <t>13.57</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW56" t="inlineStr">
         <is>
-          <t>20.60%</t>
+          <t>22.64%</t>
         </is>
       </c>
       <c r="BX56" t="inlineStr">
         <is>
-          <t>13.03%</t>
+          <t>13.16%</t>
         </is>
       </c>
       <c r="BY56" t="inlineStr">
@@ -24026,64 +24022,64 @@
       </c>
       <c r="BZ56" t="inlineStr">
         <is>
-          <t>21905</t>
+          <t>170279</t>
         </is>
       </c>
       <c r="CA56" t="inlineStr">
         <is>
-          <t>預拌混凝土64.00%、水泥22.00%、石膏板14.00% (2024年)</t>
+          <t>水泥,預拌混擬土76.31%、電力供給及儲能,可充式鋰離20.52%、海陸運輸3.17% (2024年)</t>
         </is>
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>環泥-水泥工業-上市</t>
+          <t>台泥-水泥工業-上市</t>
         </is>
       </c>
       <c r="CC56" t="inlineStr">
         <is>
-          <t>水泥工業右上上市</t>
+          <t>水泥工業右下上市</t>
         </is>
       </c>
       <c r="CD56" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="CE56" t="inlineStr">
         <is>
-          <t>31.2</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CF56" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>20.95</t>
         </is>
       </c>
       <c r="CG56" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="CH56" t="inlineStr">
         <is>
-          <t>33.81</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="CI56" t="inlineStr">
         <is>
-          <t>** 水泥 - 水泥成品、預拌混凝土</t>
+          <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
         </is>
       </c>
       <c r="CJ56" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -24093,12 +24089,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>15342.295</t>
+          <t>45105.494</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -24108,7 +24104,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -24118,7 +24114,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -24128,7 +24124,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>-22.90</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -24193,7 +24189,7 @@
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>-35.20</t>
+          <t>-39.08</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
@@ -24203,17 +24199,17 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>8.10</t>
+          <t>23.81</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
@@ -24234,56 +24230,56 @@
       </c>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>43.24</t>
         </is>
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>22.52</t>
         </is>
       </c>
       <c r="AH57" t="n">
-        <v>-1.01</v>
+        <v>2.22</v>
       </c>
       <c r="AI57" t="n">
-        <v>4.1</v>
+        <v>-3.86</v>
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-4.29</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AL57" t="inlineStr">
         <is>
-          <t>22.78</t>
+          <t>20.74</t>
         </is>
       </c>
       <c r="AM57" t="n">
-        <v>21.88</v>
+        <v>21.57</v>
       </c>
       <c r="AN57" t="n">
-        <v>22.47</v>
+        <v>22.54</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>22.65</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>1735.46</t>
+          <t>-11.17</t>
         </is>
       </c>
       <c r="AQ57" t="n">
-        <v>0.17</v>
+        <v>-0.52</v>
       </c>
       <c r="AR57" t="n">
-        <v>-0.01</v>
+        <v>-0.46</v>
       </c>
       <c r="AS57" t="inlineStr">
         <is>
@@ -24292,7 +24288,7 @@
       </c>
       <c r="AT57" t="inlineStr">
         <is>
-          <t>-101.21</t>
+          <t>-152.69</t>
         </is>
       </c>
       <c r="AU57" t="inlineStr">
@@ -24307,38 +24303,38 @@
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>348371516.0</t>
+          <t>952963874.0</t>
         </is>
       </c>
       <c r="AX57" t="n">
-        <v>469675041</v>
+        <v>684968154</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>609149921.7</t>
+          <t>608460649.9</t>
         </is>
       </c>
       <c r="AZ57" t="n">
-        <v>595644091.12</v>
+        <v>745292054.98</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>-139474880</t>
+          <t>76507504</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
         <is>
-          <t>6468947.045829888</t>
+          <t>-4038759.248015933</t>
         </is>
       </c>
       <c r="BC57" t="inlineStr">
         <is>
-          <t>-26436125.46436095</t>
+          <t>33234298.58837593</t>
         </is>
       </c>
       <c r="BD57" t="inlineStr">
         <is>
-          <t>348371516.0</t>
+          <t>952963874.0</t>
         </is>
       </c>
       <c r="BE57" t="inlineStr">
@@ -24358,7 +24354,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-7.63</t>
         </is>
       </c>
       <c r="BI57" t="inlineStr">
@@ -24403,7 +24399,7 @@
       </c>
       <c r="BQ57" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR57" t="inlineStr">
@@ -24413,7 +24409,7 @@
       </c>
       <c r="BS57" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BT57" t="inlineStr">
@@ -24468,22 +24464,22 @@
       </c>
       <c r="CD57" t="inlineStr">
         <is>
-          <t>22.7</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CE57" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CF57" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CG57" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="CH57" t="inlineStr">
@@ -24497,4226 +24493,6 @@
         </is>
       </c>
       <c r="CJ57" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>【d1】</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>1101</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>-1.09</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>22930.834</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>22.7</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>-0.67</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>2.43</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>-15.17</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>-99.0</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>2025-02-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>2025-03-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>2024-11-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>2024-12-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>34.95</t>
-        </is>
-      </c>
-      <c r="R58" t="inlineStr">
-        <is>
-          <t>34.8</t>
-        </is>
-      </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>33.4</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>33.55</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>-34.77</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>4.17</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>12.10</t>
-        </is>
-      </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr"/>
-      <c r="AD58" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="AE58" t="inlineStr">
-        <is>
-          <t>15342</t>
-        </is>
-      </c>
-      <c r="AF58" t="inlineStr">
-        <is>
-          <t>85.71</t>
-        </is>
-      </c>
-      <c r="AG58" t="inlineStr">
-        <is>
-          <t>95.24</t>
-        </is>
-      </c>
-      <c r="AH58" t="n">
-        <v>-0.57</v>
-      </c>
-      <c r="AI58" t="n">
-        <v>4.49</v>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>-2.86</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>-0.83</t>
-        </is>
-      </c>
-      <c r="AL58" t="inlineStr">
-        <is>
-          <t>22.83</t>
-        </is>
-      </c>
-      <c r="AM58" t="n">
-        <v>21.85</v>
-      </c>
-      <c r="AN58" t="n">
-        <v>22.49</v>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>22.68</t>
-        </is>
-      </c>
-      <c r="AP58" t="inlineStr">
-        <is>
-          <t>397.30</t>
-        </is>
-      </c>
-      <c r="AQ58" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AR58" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="AS58" t="inlineStr">
-        <is>
-          <t>0.88</t>
-        </is>
-      </c>
-      <c r="AT58" t="inlineStr">
-        <is>
-          <t>-106.47</t>
-        </is>
-      </c>
-      <c r="AU58" t="inlineStr">
-        <is>
-          <t>2025/11/26</t>
-        </is>
-      </c>
-      <c r="AV58" t="inlineStr">
-        <is>
-          <t>991000616.0425532</t>
-        </is>
-      </c>
-      <c r="AW58" t="inlineStr">
-        <is>
-          <t>518462876.0</t>
-        </is>
-      </c>
-      <c r="AX58" t="n">
-        <v>568040850</v>
-      </c>
-      <c r="AY58" t="inlineStr">
-        <is>
-          <t>669609157.5</t>
-        </is>
-      </c>
-      <c r="AZ58" t="n">
-        <v>620096910.86</v>
-      </c>
-      <c r="BA58" t="inlineStr">
-        <is>
-          <t>-101568307</t>
-        </is>
-      </c>
-      <c r="BB58" t="inlineStr">
-        <is>
-          <t>12451687.50222822</t>
-        </is>
-      </c>
-      <c r="BC58" t="inlineStr">
-        <is>
-          <t>-8393825.69001174</t>
-        </is>
-      </c>
-      <c r="BD58" t="inlineStr">
-        <is>
-          <t>518462876.0</t>
-        </is>
-      </c>
-      <c r="BE58" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF58" t="inlineStr">
-        <is>
-          <t>22.95</t>
-        </is>
-      </c>
-      <c r="BG58" t="inlineStr">
-        <is>
-          <t>2025/10/15</t>
-        </is>
-      </c>
-      <c r="BH58" t="inlineStr">
-        <is>
-          <t>-1.09</t>
-        </is>
-      </c>
-      <c r="BI58" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="BJ58" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="BK58" t="inlineStr">
-        <is>
-          <t>水泥工業</t>
-        </is>
-      </c>
-      <c r="BL58" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM58" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
-      </c>
-      <c r="BN58" t="inlineStr">
-        <is>
-          <t>4.325437847889285</t>
-        </is>
-      </c>
-      <c r="BO58" t="inlineStr">
-        <is>
-          <t>-14.68663446383302</t>
-        </is>
-      </c>
-      <c r="BP58" t="inlineStr">
-        <is>
-          <t>1.195709166622471</t>
-        </is>
-      </c>
-      <c r="BQ58" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR58" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS58" t="inlineStr">
-        <is>
-          <t>0.78</t>
-        </is>
-      </c>
-      <c r="BT58" t="inlineStr">
-        <is>
-          <t>4.43</t>
-        </is>
-      </c>
-      <c r="BU58" t="inlineStr">
-        <is>
-          <t>5.08</t>
-        </is>
-      </c>
-      <c r="BV58" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW58" t="inlineStr">
-        <is>
-          <t>22.64%</t>
-        </is>
-      </c>
-      <c r="BX58" t="inlineStr">
-        <is>
-          <t>13.16%</t>
-        </is>
-      </c>
-      <c r="BY58" t="inlineStr">
-        <is>
-          <t>20.16</t>
-        </is>
-      </c>
-      <c r="BZ58" t="inlineStr">
-        <is>
-          <t>170279</t>
-        </is>
-      </c>
-      <c r="CA58" t="inlineStr">
-        <is>
-          <t>水泥,預拌混擬土76.31%、電力供給及儲能,可充式鋰離20.52%、海陸運輸3.17% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB58" t="inlineStr">
-        <is>
-          <t>台泥-水泥工業-上市</t>
-        </is>
-      </c>
-      <c r="CC58" t="inlineStr">
-        <is>
-          <t>水泥工業右下上市</t>
-        </is>
-      </c>
-      <c r="CD58" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
-      <c r="CE58" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
-      <c r="CF58" t="inlineStr">
-        <is>
-          <t>22.4</t>
-        </is>
-      </c>
-      <c r="CG58" t="inlineStr">
-        <is>
-          <t>22.7</t>
-        </is>
-      </c>
-      <c r="CH58" t="inlineStr">
-        <is>
-          <t>29.05</t>
-        </is>
-      </c>
-      <c r="CI58" t="inlineStr">
-        <is>
-          <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
-        </is>
-      </c>
-      <c r="CJ58" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>【d1】</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>1101</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>0.22</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>23246.432</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>22.95</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>-1.77</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>2.43</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>5.35</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>-99.0</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>2025-02-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>2025-03-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>2024-11-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>2024-12-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>34.95</t>
-        </is>
-      </c>
-      <c r="R59" t="inlineStr">
-        <is>
-          <t>34.8</t>
-        </is>
-      </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>33.4</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>33.55</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>-34.05</t>
-        </is>
-      </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>4.17</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>2025-12-04</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>12.27</t>
-        </is>
-      </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>-1.31</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr"/>
-      <c r="AD59" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="AE59" t="inlineStr">
-        <is>
-          <t>15342</t>
-        </is>
-      </c>
-      <c r="AF59" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AG59" t="inlineStr">
-        <is>
-          <t>99.28</t>
-        </is>
-      </c>
-      <c r="AH59" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="AI59" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>-3.23</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>-0.77</t>
-        </is>
-      </c>
-      <c r="AL59" t="inlineStr">
-        <is>
-          <t>22.86</t>
-        </is>
-      </c>
-      <c r="AM59" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="AN59" t="n">
-        <v>22.53</v>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>22.7</t>
-        </is>
-      </c>
-      <c r="AP59" t="inlineStr">
-        <is>
-          <t>227.74</t>
-        </is>
-      </c>
-      <c r="AQ59" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AR59" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="AS59" t="inlineStr">
-        <is>
-          <t>0.88</t>
-        </is>
-      </c>
-      <c r="AT59" t="inlineStr">
-        <is>
-          <t>-112.90</t>
-        </is>
-      </c>
-      <c r="AU59" t="inlineStr">
-        <is>
-          <t>2025/11/26</t>
-        </is>
-      </c>
-      <c r="AV59" t="inlineStr">
-        <is>
-          <t>991000616.0425532</t>
-        </is>
-      </c>
-      <c r="AW59" t="inlineStr">
-        <is>
-          <t>537286529.0</t>
-        </is>
-      </c>
-      <c r="AX59" t="n">
-        <v>704433174.6</v>
-      </c>
-      <c r="AY59" t="inlineStr">
-        <is>
-          <t>668652391.8</t>
-        </is>
-      </c>
-      <c r="AZ59" t="n">
-        <v>679174314.1799999</v>
-      </c>
-      <c r="BA59" t="inlineStr">
-        <is>
-          <t>35780782</t>
-        </is>
-      </c>
-      <c r="BB59" t="inlineStr">
-        <is>
-          <t>16241780.80990822</t>
-        </is>
-      </c>
-      <c r="BC59" t="inlineStr">
-        <is>
-          <t>-543406.5234410763</t>
-        </is>
-      </c>
-      <c r="BD59" t="inlineStr">
-        <is>
-          <t>537286529.0</t>
-        </is>
-      </c>
-      <c r="BE59" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF59" t="inlineStr">
-        <is>
-          <t>22.95</t>
-        </is>
-      </c>
-      <c r="BG59" t="inlineStr">
-        <is>
-          <t>2025/10/15</t>
-        </is>
-      </c>
-      <c r="BH59" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="BI59" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="BJ59" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="BK59" t="inlineStr">
-        <is>
-          <t>水泥工業</t>
-        </is>
-      </c>
-      <c r="BL59" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM59" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
-      </c>
-      <c r="BN59" t="inlineStr">
-        <is>
-          <t>4.325437847889285</t>
-        </is>
-      </c>
-      <c r="BO59" t="inlineStr">
-        <is>
-          <t>-14.68663446383302</t>
-        </is>
-      </c>
-      <c r="BP59" t="inlineStr">
-        <is>
-          <t>1.195709166622471</t>
-        </is>
-      </c>
-      <c r="BQ59" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR59" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS59" t="inlineStr">
-        <is>
-          <t>0.79</t>
-        </is>
-      </c>
-      <c r="BT59" t="inlineStr">
-        <is>
-          <t>4.43</t>
-        </is>
-      </c>
-      <c r="BU59" t="inlineStr">
-        <is>
-          <t>5.08</t>
-        </is>
-      </c>
-      <c r="BV59" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW59" t="inlineStr">
-        <is>
-          <t>22.64%</t>
-        </is>
-      </c>
-      <c r="BX59" t="inlineStr">
-        <is>
-          <t>13.16%</t>
-        </is>
-      </c>
-      <c r="BY59" t="inlineStr">
-        <is>
-          <t>20.16</t>
-        </is>
-      </c>
-      <c r="BZ59" t="inlineStr">
-        <is>
-          <t>170279</t>
-        </is>
-      </c>
-      <c r="CA59" t="inlineStr">
-        <is>
-          <t>水泥,預拌混擬土76.31%、電力供給及儲能,可充式鋰離20.52%、海陸運輸3.17% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB59" t="inlineStr">
-        <is>
-          <t>台泥-水泥工業-上市</t>
-        </is>
-      </c>
-      <c r="CC59" t="inlineStr">
-        <is>
-          <t>水泥工業右下上市</t>
-        </is>
-      </c>
-      <c r="CD59" t="inlineStr">
-        <is>
-          <t>22.9</t>
-        </is>
-      </c>
-      <c r="CE59" t="inlineStr">
-        <is>
-          <t>23.3</t>
-        </is>
-      </c>
-      <c r="CF59" t="inlineStr">
-        <is>
-          <t>22.9</t>
-        </is>
-      </c>
-      <c r="CG59" t="inlineStr">
-        <is>
-          <t>22.95</t>
-        </is>
-      </c>
-      <c r="CH59" t="inlineStr">
-        <is>
-          <t>29.05</t>
-        </is>
-      </c>
-      <c r="CI59" t="inlineStr">
-        <is>
-          <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
-        </is>
-      </c>
-      <c r="CJ59" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>【d1】</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>1101</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>0.44</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>18924.305</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>22.9</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>-1.55</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>2.43</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>5.87</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>-99.0</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>2025-02-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>2025-03-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>2024-11-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>2024-12-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>34.95</t>
-        </is>
-      </c>
-      <c r="R60" t="inlineStr">
-        <is>
-          <t>34.8</t>
-        </is>
-      </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>33.4</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>33.55</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>-34.20</t>
-        </is>
-      </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>4.17</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>9.99</t>
-        </is>
-      </c>
-      <c r="AA60" t="inlineStr">
-        <is>
-          <t>0.45</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr"/>
-      <c r="AD60" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="AE60" t="inlineStr">
-        <is>
-          <t>15342</t>
-        </is>
-      </c>
-      <c r="AF60" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AG60" t="inlineStr">
-        <is>
-          <t>98.6</t>
-        </is>
-      </c>
-      <c r="AH60" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="AI60" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>-3.59</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>-0.81</t>
-        </is>
-      </c>
-      <c r="AL60" t="inlineStr">
-        <is>
-          <t>22.69</t>
-        </is>
-      </c>
-      <c r="AM60" t="n">
-        <v>21.73</v>
-      </c>
-      <c r="AN60" t="n">
-        <v>22.54</v>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>22.72</t>
-        </is>
-      </c>
-      <c r="AP60" t="inlineStr">
-        <is>
-          <t>148.50</t>
-        </is>
-      </c>
-      <c r="AQ60" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AR60" t="n">
-        <v>-0.18</v>
-      </c>
-      <c r="AS60" t="inlineStr">
-        <is>
-          <t>0.88</t>
-        </is>
-      </c>
-      <c r="AT60" t="inlineStr">
-        <is>
-          <t>-120.25</t>
-        </is>
-      </c>
-      <c r="AU60" t="inlineStr">
-        <is>
-          <t>2025/11/26</t>
-        </is>
-      </c>
-      <c r="AV60" t="inlineStr">
-        <is>
-          <t>991000616.0425532</t>
-        </is>
-      </c>
-      <c r="AW60" t="inlineStr">
-        <is>
-          <t>432691470.0</t>
-        </is>
-      </c>
-      <c r="AX60" t="n">
-        <v>704226090.4</v>
-      </c>
-      <c r="AY60" t="inlineStr">
-        <is>
-          <t>665210810.6</t>
-        </is>
-      </c>
-      <c r="AZ60" t="n">
-        <v>756181820.36</v>
-      </c>
-      <c r="BA60" t="inlineStr">
-        <is>
-          <t>39015279</t>
-        </is>
-      </c>
-      <c r="BB60" t="inlineStr">
-        <is>
-          <t>19293633.05233536</t>
-        </is>
-      </c>
-      <c r="BC60" t="inlineStr">
-        <is>
-          <t>8674065.41178286</t>
-        </is>
-      </c>
-      <c r="BD60" t="inlineStr">
-        <is>
-          <t>432691470.0</t>
-        </is>
-      </c>
-      <c r="BE60" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF60" t="inlineStr">
-        <is>
-          <t>22.95</t>
-        </is>
-      </c>
-      <c r="BG60" t="inlineStr">
-        <is>
-          <t>2025/10/15</t>
-        </is>
-      </c>
-      <c r="BH60" t="inlineStr">
-        <is>
-          <t>-0.22</t>
-        </is>
-      </c>
-      <c r="BI60" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="BJ60" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="BK60" t="inlineStr">
-        <is>
-          <t>水泥工業</t>
-        </is>
-      </c>
-      <c r="BL60" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM60" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
-      </c>
-      <c r="BN60" t="inlineStr">
-        <is>
-          <t>4.325437847889285</t>
-        </is>
-      </c>
-      <c r="BO60" t="inlineStr">
-        <is>
-          <t>-14.68663446383302</t>
-        </is>
-      </c>
-      <c r="BP60" t="inlineStr">
-        <is>
-          <t>1.195709166622471</t>
-        </is>
-      </c>
-      <c r="BQ60" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR60" t="inlineStr">
-        <is>
-          <t>價-量縮</t>
-        </is>
-      </c>
-      <c r="BS60" t="inlineStr">
-        <is>
-          <t>0.79</t>
-        </is>
-      </c>
-      <c r="BT60" t="inlineStr">
-        <is>
-          <t>4.43</t>
-        </is>
-      </c>
-      <c r="BU60" t="inlineStr">
-        <is>
-          <t>5.08</t>
-        </is>
-      </c>
-      <c r="BV60" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW60" t="inlineStr">
-        <is>
-          <t>22.64%</t>
-        </is>
-      </c>
-      <c r="BX60" t="inlineStr">
-        <is>
-          <t>13.16%</t>
-        </is>
-      </c>
-      <c r="BY60" t="inlineStr">
-        <is>
-          <t>20.16</t>
-        </is>
-      </c>
-      <c r="BZ60" t="inlineStr">
-        <is>
-          <t>170279</t>
-        </is>
-      </c>
-      <c r="CA60" t="inlineStr">
-        <is>
-          <t>水泥,預拌混擬土76.31%、電力供給及儲能,可充式鋰離20.52%、海陸運輸3.17% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB60" t="inlineStr">
-        <is>
-          <t>台泥-水泥工業-上市</t>
-        </is>
-      </c>
-      <c r="CC60" t="inlineStr">
-        <is>
-          <t>水泥工業右下上市</t>
-        </is>
-      </c>
-      <c r="CD60" t="inlineStr">
-        <is>
-          <t>22.85</t>
-        </is>
-      </c>
-      <c r="CE60" t="inlineStr">
-        <is>
-          <t>23.05</t>
-        </is>
-      </c>
-      <c r="CF60" t="inlineStr">
-        <is>
-          <t>22.65</t>
-        </is>
-      </c>
-      <c r="CG60" t="inlineStr">
-        <is>
-          <t>22.9</t>
-        </is>
-      </c>
-      <c r="CH60" t="inlineStr">
-        <is>
-          <t>29.05</t>
-        </is>
-      </c>
-      <c r="CI60" t="inlineStr">
-        <is>
-          <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
-        </is>
-      </c>
-      <c r="CJ60" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>【d1】</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>1101</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>22416.9</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>22.8</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>-1.11</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>2.43</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>8.03</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>-99.0</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>2025-02-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>2025-03-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>2024-11-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>2024-12-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>34.95</t>
-        </is>
-      </c>
-      <c r="R61" t="inlineStr">
-        <is>
-          <t>34.8</t>
-        </is>
-      </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>33.4</t>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>33.55</t>
-        </is>
-      </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>-34.48</t>
-        </is>
-      </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>4.17</t>
-        </is>
-      </c>
-      <c r="Y61" t="inlineStr">
-        <is>
-          <t>2025-12-02</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>11.83</t>
-        </is>
-      </c>
-      <c r="AA61" t="inlineStr">
-        <is>
-          <t>-0.44</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr"/>
-      <c r="AD61" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="AE61" t="inlineStr">
-        <is>
-          <t>15342</t>
-        </is>
-      </c>
-      <c r="AF61" t="inlineStr">
-        <is>
-          <t>97.83</t>
-        </is>
-      </c>
-      <c r="AG61" t="inlineStr">
-        <is>
-          <t>98.6</t>
-        </is>
-      </c>
-      <c r="AH61" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI61" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>-3.93</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>-0.95</t>
-        </is>
-      </c>
-      <c r="AL61" t="inlineStr">
-        <is>
-          <t>22.5</t>
-        </is>
-      </c>
-      <c r="AM61" t="n">
-        <v>21.64</v>
-      </c>
-      <c r="AN61" t="n">
-        <v>22.52</v>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>22.74</t>
-        </is>
-      </c>
-      <c r="AP61" t="inlineStr">
-        <is>
-          <t>106.33</t>
-        </is>
-      </c>
-      <c r="AQ61" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AR61" t="n">
-        <v>-0.24</v>
-      </c>
-      <c r="AS61" t="inlineStr">
-        <is>
-          <t>0.88</t>
-        </is>
-      </c>
-      <c r="AT61" t="inlineStr">
-        <is>
-          <t>-127.77</t>
-        </is>
-      </c>
-      <c r="AU61" t="inlineStr">
-        <is>
-          <t>2025/11/26</t>
-        </is>
-      </c>
-      <c r="AV61" t="inlineStr">
-        <is>
-          <t>991000616.0425532</t>
-        </is>
-      </c>
-      <c r="AW61" t="inlineStr">
-        <is>
-          <t>511562814.0</t>
-        </is>
-      </c>
-      <c r="AX61" t="n">
-        <v>752025237.4</v>
-      </c>
-      <c r="AY61" t="inlineStr">
-        <is>
-          <t>696109315.3</t>
-        </is>
-      </c>
-      <c r="AZ61" t="n">
-        <v>757139109.14</v>
-      </c>
-      <c r="BA61" t="inlineStr">
-        <is>
-          <t>55915922</t>
-        </is>
-      </c>
-      <c r="BB61" t="inlineStr">
-        <is>
-          <t>21224463.53243582</t>
-        </is>
-      </c>
-      <c r="BC61" t="inlineStr">
-        <is>
-          <t>32738707.87596762</t>
-        </is>
-      </c>
-      <c r="BD61" t="inlineStr">
-        <is>
-          <t>511562814.0</t>
-        </is>
-      </c>
-      <c r="BE61" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF61" t="inlineStr">
-        <is>
-          <t>22.95</t>
-        </is>
-      </c>
-      <c r="BG61" t="inlineStr">
-        <is>
-          <t>2025/10/15</t>
-        </is>
-      </c>
-      <c r="BH61" t="inlineStr">
-        <is>
-          <t>-0.65</t>
-        </is>
-      </c>
-      <c r="BI61" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="BJ61" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="BK61" t="inlineStr">
-        <is>
-          <t>水泥工業</t>
-        </is>
-      </c>
-      <c r="BL61" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM61" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
-      </c>
-      <c r="BN61" t="inlineStr">
-        <is>
-          <t>4.325437847889285</t>
-        </is>
-      </c>
-      <c r="BO61" t="inlineStr">
-        <is>
-          <t>-14.68663446383302</t>
-        </is>
-      </c>
-      <c r="BP61" t="inlineStr">
-        <is>
-          <t>1.195709166622471</t>
-        </is>
-      </c>
-      <c r="BQ61" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR61" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS61" t="inlineStr">
-        <is>
-          <t>0.78</t>
-        </is>
-      </c>
-      <c r="BT61" t="inlineStr">
-        <is>
-          <t>4.43</t>
-        </is>
-      </c>
-      <c r="BU61" t="inlineStr">
-        <is>
-          <t>5.08</t>
-        </is>
-      </c>
-      <c r="BV61" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW61" t="inlineStr">
-        <is>
-          <t>22.64%</t>
-        </is>
-      </c>
-      <c r="BX61" t="inlineStr">
-        <is>
-          <t>13.16%</t>
-        </is>
-      </c>
-      <c r="BY61" t="inlineStr">
-        <is>
-          <t>20.16</t>
-        </is>
-      </c>
-      <c r="BZ61" t="inlineStr">
-        <is>
-          <t>170279</t>
-        </is>
-      </c>
-      <c r="CA61" t="inlineStr">
-        <is>
-          <t>水泥,預拌混擬土76.31%、電力供給及儲能,可充式鋰離20.52%、海陸運輸3.17% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB61" t="inlineStr">
-        <is>
-          <t>台泥-水泥工業-上市</t>
-        </is>
-      </c>
-      <c r="CC61" t="inlineStr">
-        <is>
-          <t>水泥工業右下上市</t>
-        </is>
-      </c>
-      <c r="CD61" t="inlineStr">
-        <is>
-          <t>22.9</t>
-        </is>
-      </c>
-      <c r="CE61" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
-      <c r="CF61" t="inlineStr">
-        <is>
-          <t>22.7</t>
-        </is>
-      </c>
-      <c r="CG61" t="inlineStr">
-        <is>
-          <t>22.8</t>
-        </is>
-      </c>
-      <c r="CH61" t="inlineStr">
-        <is>
-          <t>29.05</t>
-        </is>
-      </c>
-      <c r="CI61" t="inlineStr">
-        <is>
-          <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
-        </is>
-      </c>
-      <c r="CJ61" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>【d1】</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>1101</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>-0.22</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>36403.182</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>22.8</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>-1.11</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>2.43</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>4.44</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>-99.0</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>2025-02-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>2025-03-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>2024-11-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>2024-12-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>34.95</t>
-        </is>
-      </c>
-      <c r="R62" t="inlineStr">
-        <is>
-          <t>34.8</t>
-        </is>
-      </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>33.4</t>
-        </is>
-      </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>33.55</t>
-        </is>
-      </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>-34.48</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>4.17</t>
-        </is>
-      </c>
-      <c r="Y62" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>19.21</t>
-        </is>
-      </c>
-      <c r="AA62" t="inlineStr">
-        <is>
-          <t>-2.63</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr"/>
-      <c r="AD62" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="AE62" t="inlineStr">
-        <is>
-          <t>15342</t>
-        </is>
-      </c>
-      <c r="AF62" t="inlineStr">
-        <is>
-          <t>97.96</t>
-        </is>
-      </c>
-      <c r="AG62" t="inlineStr">
-        <is>
-          <t>99.32</t>
-        </is>
-      </c>
-      <c r="AH62" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AI62" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>-4.26</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>-1.08</t>
-        </is>
-      </c>
-      <c r="AL62" t="inlineStr">
-        <is>
-          <t>22.18</t>
-        </is>
-      </c>
-      <c r="AM62" t="n">
-        <v>21.56</v>
-      </c>
-      <c r="AN62" t="n">
-        <v>22.51</v>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>22.76</t>
-        </is>
-      </c>
-      <c r="AP62" t="inlineStr">
-        <is>
-          <t>78.93</t>
-        </is>
-      </c>
-      <c r="AQ62" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="AR62" t="n">
-        <v>-0.31</v>
-      </c>
-      <c r="AS62" t="inlineStr">
-        <is>
-          <t>0.88</t>
-        </is>
-      </c>
-      <c r="AT62" t="inlineStr">
-        <is>
-          <t>-135.15</t>
-        </is>
-      </c>
-      <c r="AU62" t="inlineStr">
-        <is>
-          <t>2025/11/26</t>
-        </is>
-      </c>
-      <c r="AV62" t="inlineStr">
-        <is>
-          <t>991000616.0425532</t>
-        </is>
-      </c>
-      <c r="AW62" t="inlineStr">
-        <is>
-          <t>840200561.0</t>
-        </is>
-      </c>
-      <c r="AX62" t="n">
-        <v>748624802.4</v>
-      </c>
-      <c r="AY62" t="inlineStr">
-        <is>
-          <t>716796478.2</t>
-        </is>
-      </c>
-      <c r="AZ62" t="n">
-        <v>757710850.26</v>
-      </c>
-      <c r="BA62" t="inlineStr">
-        <is>
-          <t>31828324</t>
-        </is>
-      </c>
-      <c r="BB62" t="inlineStr">
-        <is>
-          <t>19130964.56088458</t>
-        </is>
-      </c>
-      <c r="BC62" t="inlineStr">
-        <is>
-          <t>57497027.82923281</t>
-        </is>
-      </c>
-      <c r="BD62" t="inlineStr">
-        <is>
-          <t>840200561.0</t>
-        </is>
-      </c>
-      <c r="BE62" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF62" t="inlineStr">
-        <is>
-          <t>22.95</t>
-        </is>
-      </c>
-      <c r="BG62" t="inlineStr">
-        <is>
-          <t>2025/10/15</t>
-        </is>
-      </c>
-      <c r="BH62" t="inlineStr">
-        <is>
-          <t>-0.65</t>
-        </is>
-      </c>
-      <c r="BI62" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="BJ62" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="BK62" t="inlineStr">
-        <is>
-          <t>水泥工業</t>
-        </is>
-      </c>
-      <c r="BL62" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM62" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
-      </c>
-      <c r="BN62" t="inlineStr">
-        <is>
-          <t>4.325437847889285</t>
-        </is>
-      </c>
-      <c r="BO62" t="inlineStr">
-        <is>
-          <t>-14.68663446383302</t>
-        </is>
-      </c>
-      <c r="BP62" t="inlineStr">
-        <is>
-          <t>1.195709166622471</t>
-        </is>
-      </c>
-      <c r="BQ62" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR62" t="inlineStr">
-        <is>
-          <t>價跌量增</t>
-        </is>
-      </c>
-      <c r="BS62" t="inlineStr">
-        <is>
-          <t>0.78</t>
-        </is>
-      </c>
-      <c r="BT62" t="inlineStr">
-        <is>
-          <t>4.43</t>
-        </is>
-      </c>
-      <c r="BU62" t="inlineStr">
-        <is>
-          <t>5.08</t>
-        </is>
-      </c>
-      <c r="BV62" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW62" t="inlineStr">
-        <is>
-          <t>22.64%</t>
-        </is>
-      </c>
-      <c r="BX62" t="inlineStr">
-        <is>
-          <t>13.16%</t>
-        </is>
-      </c>
-      <c r="BY62" t="inlineStr">
-        <is>
-          <t>20.16</t>
-        </is>
-      </c>
-      <c r="BZ62" t="inlineStr">
-        <is>
-          <t>170279</t>
-        </is>
-      </c>
-      <c r="CA62" t="inlineStr">
-        <is>
-          <t>水泥,預拌混擬土76.31%、電力供給及儲能,可充式鋰離20.52%、海陸運輸3.17% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB62" t="inlineStr">
-        <is>
-          <t>台泥-水泥工業-上市</t>
-        </is>
-      </c>
-      <c r="CC62" t="inlineStr">
-        <is>
-          <t>水泥工業右下上市</t>
-        </is>
-      </c>
-      <c r="CD62" t="inlineStr">
-        <is>
-          <t>22.85</t>
-        </is>
-      </c>
-      <c r="CE62" t="inlineStr">
-        <is>
-          <t>23.45</t>
-        </is>
-      </c>
-      <c r="CF62" t="inlineStr">
-        <is>
-          <t>22.75</t>
-        </is>
-      </c>
-      <c r="CG62" t="inlineStr">
-        <is>
-          <t>22.8</t>
-        </is>
-      </c>
-      <c r="CH62" t="inlineStr">
-        <is>
-          <t>29.05</t>
-        </is>
-      </c>
-      <c r="CI62" t="inlineStr">
-        <is>
-          <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
-        </is>
-      </c>
-      <c r="CJ62" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>【d1】</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>1101</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>3.33</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>52859.34</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>22.85</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>-1.33</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>2.43</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>14.80</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>-99.0</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>2025-02-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>2025-03-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>2024-11-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>2024-12-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>34.95</t>
-        </is>
-      </c>
-      <c r="R63" t="inlineStr">
-        <is>
-          <t>34.8</t>
-        </is>
-      </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>33.4</t>
-        </is>
-      </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>33.55</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>-34.34</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>4.17</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>27.90</t>
-        </is>
-      </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr"/>
-      <c r="AD63" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="AE63" t="inlineStr">
-        <is>
-          <t>15342</t>
-        </is>
-      </c>
-      <c r="AF63" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AG63" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AH63" t="n">
-        <v>4.53</v>
-      </c>
-      <c r="AI63" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>-4.5</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>-1.22</t>
-        </is>
-      </c>
-      <c r="AL63" t="inlineStr">
-        <is>
-          <t>21.86</t>
-        </is>
-      </c>
-      <c r="AM63" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="AN63" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>22.78</t>
-        </is>
-      </c>
-      <c r="AP63" t="inlineStr">
-        <is>
-          <t>54.87</t>
-        </is>
-      </c>
-      <c r="AQ63" t="n">
-        <v>-0.17</v>
-      </c>
-      <c r="AR63" t="n">
-        <v>-0.37</v>
-      </c>
-      <c r="AS63" t="inlineStr">
-        <is>
-          <t>0.88</t>
-        </is>
-      </c>
-      <c r="AT63" t="inlineStr">
-        <is>
-          <t>-142.09</t>
-        </is>
-      </c>
-      <c r="AU63" t="inlineStr">
-        <is>
-          <t>2025/11/26</t>
-        </is>
-      </c>
-      <c r="AV63" t="inlineStr">
-        <is>
-          <t>991000616.0425532</t>
-        </is>
-      </c>
-      <c r="AW63" t="inlineStr">
-        <is>
-          <t>1200424499.0</t>
-        </is>
-      </c>
-      <c r="AX63" t="n">
-        <v>771177465</v>
-      </c>
-      <c r="AY63" t="inlineStr">
-        <is>
-          <t>671756204.4</t>
-        </is>
-      </c>
-      <c r="AZ63" t="n">
-        <v>746928524.46</v>
-      </c>
-      <c r="BA63" t="inlineStr">
-        <is>
-          <t>99421260</t>
-        </is>
-      </c>
-      <c r="BB63" t="inlineStr">
-        <is>
-          <t>12155316.69391218</t>
-        </is>
-      </c>
-      <c r="BC63" t="inlineStr">
-        <is>
-          <t>55601403.87571049</t>
-        </is>
-      </c>
-      <c r="BD63" t="inlineStr">
-        <is>
-          <t>1200424499.0</t>
-        </is>
-      </c>
-      <c r="BE63" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF63" t="inlineStr">
-        <is>
-          <t>22.95</t>
-        </is>
-      </c>
-      <c r="BG63" t="inlineStr">
-        <is>
-          <t>2025/10/15</t>
-        </is>
-      </c>
-      <c r="BH63" t="inlineStr">
-        <is>
-          <t>-0.44</t>
-        </is>
-      </c>
-      <c r="BI63" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="BJ63" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="BK63" t="inlineStr">
-        <is>
-          <t>水泥工業</t>
-        </is>
-      </c>
-      <c r="BL63" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM63" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
-      </c>
-      <c r="BN63" t="inlineStr">
-        <is>
-          <t>4.325437847889285</t>
-        </is>
-      </c>
-      <c r="BO63" t="inlineStr">
-        <is>
-          <t>-14.68663446383302</t>
-        </is>
-      </c>
-      <c r="BP63" t="inlineStr">
-        <is>
-          <t>1.195709166622471</t>
-        </is>
-      </c>
-      <c r="BQ63" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
-        </is>
-      </c>
-      <c r="BR63" t="inlineStr">
-        <is>
-          <t>價漲量增</t>
-        </is>
-      </c>
-      <c r="BS63" t="inlineStr">
-        <is>
-          <t>0.79</t>
-        </is>
-      </c>
-      <c r="BT63" t="inlineStr">
-        <is>
-          <t>4.43</t>
-        </is>
-      </c>
-      <c r="BU63" t="inlineStr">
-        <is>
-          <t>5.08</t>
-        </is>
-      </c>
-      <c r="BV63" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW63" t="inlineStr">
-        <is>
-          <t>22.64%</t>
-        </is>
-      </c>
-      <c r="BX63" t="inlineStr">
-        <is>
-          <t>13.16%</t>
-        </is>
-      </c>
-      <c r="BY63" t="inlineStr">
-        <is>
-          <t>20.16</t>
-        </is>
-      </c>
-      <c r="BZ63" t="inlineStr">
-        <is>
-          <t>170279</t>
-        </is>
-      </c>
-      <c r="CA63" t="inlineStr">
-        <is>
-          <t>水泥,預拌混擬土76.31%、電力供給及儲能,可充式鋰離20.52%、海陸運輸3.17% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB63" t="inlineStr">
-        <is>
-          <t>台泥-水泥工業-上市</t>
-        </is>
-      </c>
-      <c r="CC63" t="inlineStr">
-        <is>
-          <t>水泥工業右下上市</t>
-        </is>
-      </c>
-      <c r="CD63" t="inlineStr">
-        <is>
-          <t>22.5</t>
-        </is>
-      </c>
-      <c r="CE63" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
-      <c r="CF63" t="inlineStr">
-        <is>
-          <t>22.35</t>
-        </is>
-      </c>
-      <c r="CG63" t="inlineStr">
-        <is>
-          <t>22.85</t>
-        </is>
-      </c>
-      <c r="CH63" t="inlineStr">
-        <is>
-          <t>29.05</t>
-        </is>
-      </c>
-      <c r="CI63" t="inlineStr">
-        <is>
-          <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
-        </is>
-      </c>
-      <c r="CJ63" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>【d2】</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>1101</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>0.69</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>24336.287</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>22.1</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>2.43</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>3.89</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>-99.0</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>2025-02-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>2025-03-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>2024-11-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>2024-12-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t>34.95</t>
-        </is>
-      </c>
-      <c r="R64" t="inlineStr">
-        <is>
-          <t>34.8</t>
-        </is>
-      </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>33.4</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>33.55</t>
-        </is>
-      </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>-36.49</t>
-        </is>
-      </c>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t>4.17</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>12.84</t>
-        </is>
-      </c>
-      <c r="AA64" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr"/>
-      <c r="AD64" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="AE64" t="inlineStr">
-        <is>
-          <t>15342</t>
-        </is>
-      </c>
-      <c r="AF64" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AG64" t="inlineStr">
-        <is>
-          <t>84.44</t>
-        </is>
-      </c>
-      <c r="AH64" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="AI64" t="n">
-        <v>-0.24</v>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>-4.62</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>-1.33</t>
-        </is>
-      </c>
-      <c r="AL64" t="inlineStr">
-        <is>
-          <t>21.4</t>
-        </is>
-      </c>
-      <c r="AM64" t="n">
-        <v>21.45</v>
-      </c>
-      <c r="AN64" t="n">
-        <v>22.49</v>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>22.8</t>
-        </is>
-      </c>
-      <c r="AP64" t="inlineStr">
-        <is>
-          <t>28.78</t>
-        </is>
-      </c>
-      <c r="AQ64" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="AR64" t="n">
-        <v>-0.42</v>
-      </c>
-      <c r="AS64" t="inlineStr">
-        <is>
-          <t>0.88</t>
-        </is>
-      </c>
-      <c r="AT64" t="inlineStr">
-        <is>
-          <t>-147.86</t>
-        </is>
-      </c>
-      <c r="AU64" t="inlineStr">
-        <is>
-          <t>2025/11/26</t>
-        </is>
-      </c>
-      <c r="AV64" t="inlineStr">
-        <is>
-          <t>991000616.0425532</t>
-        </is>
-      </c>
-      <c r="AW64" t="inlineStr">
-        <is>
-          <t>536251108.0</t>
-        </is>
-      </c>
-      <c r="AX64" t="n">
-        <v>632871609</v>
-      </c>
-      <c r="AY64" t="inlineStr">
-        <is>
-          <t>609167742.3</t>
-        </is>
-      </c>
-      <c r="AZ64" t="n">
-        <v>731439820.52</v>
-      </c>
-      <c r="BA64" t="inlineStr">
-        <is>
-          <t>23703866</t>
-        </is>
-      </c>
-      <c r="BB64" t="inlineStr">
-        <is>
-          <t>4256028.115403395</t>
-        </is>
-      </c>
-      <c r="BC64" t="inlineStr">
-        <is>
-          <t>12312183.30368912</t>
-        </is>
-      </c>
-      <c r="BD64" t="inlineStr">
-        <is>
-          <t>536251108.0</t>
-        </is>
-      </c>
-      <c r="BE64" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF64" t="inlineStr">
-        <is>
-          <t>22.95</t>
-        </is>
-      </c>
-      <c r="BG64" t="inlineStr">
-        <is>
-          <t>2025/10/15</t>
-        </is>
-      </c>
-      <c r="BH64" t="inlineStr">
-        <is>
-          <t>-3.70</t>
-        </is>
-      </c>
-      <c r="BI64" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="BJ64" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="BK64" t="inlineStr">
-        <is>
-          <t>水泥工業</t>
-        </is>
-      </c>
-      <c r="BL64" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM64" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
-      </c>
-      <c r="BN64" t="inlineStr">
-        <is>
-          <t>4.325437847889285</t>
-        </is>
-      </c>
-      <c r="BO64" t="inlineStr">
-        <is>
-          <t>-14.68663446383302</t>
-        </is>
-      </c>
-      <c r="BP64" t="inlineStr">
-        <is>
-          <t>1.195709166622471</t>
-        </is>
-      </c>
-      <c r="BQ64" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR64" t="inlineStr">
-        <is>
-          <t>價-量縮</t>
-        </is>
-      </c>
-      <c r="BS64" t="inlineStr">
-        <is>
-          <t>0.76</t>
-        </is>
-      </c>
-      <c r="BT64" t="inlineStr">
-        <is>
-          <t>4.43</t>
-        </is>
-      </c>
-      <c r="BU64" t="inlineStr">
-        <is>
-          <t>5.08</t>
-        </is>
-      </c>
-      <c r="BV64" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW64" t="inlineStr">
-        <is>
-          <t>22.64%</t>
-        </is>
-      </c>
-      <c r="BX64" t="inlineStr">
-        <is>
-          <t>13.16%</t>
-        </is>
-      </c>
-      <c r="BY64" t="inlineStr">
-        <is>
-          <t>20.16</t>
-        </is>
-      </c>
-      <c r="BZ64" t="inlineStr">
-        <is>
-          <t>170279</t>
-        </is>
-      </c>
-      <c r="CA64" t="inlineStr">
-        <is>
-          <t>水泥,預拌混擬土76.31%、電力供給及儲能,可充式鋰離20.52%、海陸運輸3.17% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB64" t="inlineStr">
-        <is>
-          <t>台泥-水泥工業-上市</t>
-        </is>
-      </c>
-      <c r="CC64" t="inlineStr">
-        <is>
-          <t>水泥工業右下上市</t>
-        </is>
-      </c>
-      <c r="CD64" t="inlineStr">
-        <is>
-          <t>21.85</t>
-        </is>
-      </c>
-      <c r="CE64" t="inlineStr">
-        <is>
-          <t>22.15</t>
-        </is>
-      </c>
-      <c r="CF64" t="inlineStr">
-        <is>
-          <t>21.75</t>
-        </is>
-      </c>
-      <c r="CG64" t="inlineStr">
-        <is>
-          <t>22.1</t>
-        </is>
-      </c>
-      <c r="CH64" t="inlineStr">
-        <is>
-          <t>29.05</t>
-        </is>
-      </c>
-      <c r="CI64" t="inlineStr">
-        <is>
-          <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
-        </is>
-      </c>
-      <c r="CJ64" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>【d2】</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>1101</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>3.51</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>30791.526</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>21.95</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>2.66</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>2.43</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>-99.0</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>2025-02-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>2025-03-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>2024-11-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>2024-12-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>34.95</t>
-        </is>
-      </c>
-      <c r="R65" t="inlineStr">
-        <is>
-          <t>34.8</t>
-        </is>
-      </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>33.4</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>33.55</t>
-        </is>
-      </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>-36.93</t>
-        </is>
-      </c>
-      <c r="X65" t="inlineStr">
-        <is>
-          <t>4.17</t>
-        </is>
-      </c>
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>16.25</t>
-        </is>
-      </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr"/>
-      <c r="AD65" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="AE65" t="inlineStr">
-        <is>
-          <t>15342</t>
-        </is>
-      </c>
-      <c r="AF65" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AG65" t="inlineStr">
-        <is>
-          <t>65.53</t>
-        </is>
-      </c>
-      <c r="AH65" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="AI65" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>-4.6</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>-1.42</t>
-        </is>
-      </c>
-      <c r="AL65" t="inlineStr">
-        <is>
-          <t>21.12</t>
-        </is>
-      </c>
-      <c r="AM65" t="n">
-        <v>21.46</v>
-      </c>
-      <c r="AN65" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>22.82</t>
-        </is>
-      </c>
-      <c r="AP65" t="inlineStr">
-        <is>
-          <t>13.90</t>
-        </is>
-      </c>
-      <c r="AQ65" t="n">
-        <v>-0.39</v>
-      </c>
-      <c r="AR65" t="n">
-        <v>-0.45</v>
-      </c>
-      <c r="AS65" t="inlineStr">
-        <is>
-          <t>0.88</t>
-        </is>
-      </c>
-      <c r="AT65" t="inlineStr">
-        <is>
-          <t>-151.31</t>
-        </is>
-      </c>
-      <c r="AU65" t="inlineStr">
-        <is>
-          <t>2025/11/26</t>
-        </is>
-      </c>
-      <c r="AV65" t="inlineStr">
-        <is>
-          <t>991000616.0425532</t>
-        </is>
-      </c>
-      <c r="AW65" t="inlineStr">
-        <is>
-          <t>671687205.0</t>
-        </is>
-      </c>
-      <c r="AX65" t="n">
-        <v>626195530.8</v>
-      </c>
-      <c r="AY65" t="inlineStr">
-        <is>
-          <t>622132821.3</t>
-        </is>
-      </c>
-      <c r="AZ65" t="n">
-        <v>733146356.66</v>
-      </c>
-      <c r="BA65" t="inlineStr">
-        <is>
-          <t>4062709</t>
-        </is>
-      </c>
-      <c r="BB65" t="inlineStr">
-        <is>
-          <t>2791272.626624172</t>
-        </is>
-      </c>
-      <c r="BC65" t="inlineStr">
-        <is>
-          <t>21192153.54709804</t>
-        </is>
-      </c>
-      <c r="BD65" t="inlineStr">
-        <is>
-          <t>671687205.0</t>
-        </is>
-      </c>
-      <c r="BE65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF65" t="inlineStr">
-        <is>
-          <t>22.95</t>
-        </is>
-      </c>
-      <c r="BG65" t="inlineStr">
-        <is>
-          <t>2025/10/15</t>
-        </is>
-      </c>
-      <c r="BH65" t="inlineStr">
-        <is>
-          <t>-4.36</t>
-        </is>
-      </c>
-      <c r="BI65" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="BJ65" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="BK65" t="inlineStr">
-        <is>
-          <t>水泥工業</t>
-        </is>
-      </c>
-      <c r="BL65" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM65" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
-      </c>
-      <c r="BN65" t="inlineStr">
-        <is>
-          <t>4.325437847889285</t>
-        </is>
-      </c>
-      <c r="BO65" t="inlineStr">
-        <is>
-          <t>-14.68663446383302</t>
-        </is>
-      </c>
-      <c r="BP65" t="inlineStr">
-        <is>
-          <t>1.195709166622471</t>
-        </is>
-      </c>
-      <c r="BQ65" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR65" t="inlineStr">
-        <is>
-          <t>價漲量增</t>
-        </is>
-      </c>
-      <c r="BS65" t="inlineStr">
-        <is>
-          <t>0.76</t>
-        </is>
-      </c>
-      <c r="BT65" t="inlineStr">
-        <is>
-          <t>4.43</t>
-        </is>
-      </c>
-      <c r="BU65" t="inlineStr">
-        <is>
-          <t>5.08</t>
-        </is>
-      </c>
-      <c r="BV65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW65" t="inlineStr">
-        <is>
-          <t>22.64%</t>
-        </is>
-      </c>
-      <c r="BX65" t="inlineStr">
-        <is>
-          <t>13.16%</t>
-        </is>
-      </c>
-      <c r="BY65" t="inlineStr">
-        <is>
-          <t>20.16</t>
-        </is>
-      </c>
-      <c r="BZ65" t="inlineStr">
-        <is>
-          <t>170279</t>
-        </is>
-      </c>
-      <c r="CA65" t="inlineStr">
-        <is>
-          <t>水泥,預拌混擬土76.31%、電力供給及儲能,可充式鋰離20.52%、海陸運輸3.17% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB65" t="inlineStr">
-        <is>
-          <t>台泥-水泥工業-上市</t>
-        </is>
-      </c>
-      <c r="CC65" t="inlineStr">
-        <is>
-          <t>水泥工業右下上市</t>
-        </is>
-      </c>
-      <c r="CD65" t="inlineStr">
-        <is>
-          <t>21.35</t>
-        </is>
-      </c>
-      <c r="CE65" t="inlineStr">
-        <is>
-          <t>22.05</t>
-        </is>
-      </c>
-      <c r="CF65" t="inlineStr">
-        <is>
-          <t>21.35</t>
-        </is>
-      </c>
-      <c r="CG65" t="inlineStr">
-        <is>
-          <t>21.95</t>
-        </is>
-      </c>
-      <c r="CH65" t="inlineStr">
-        <is>
-          <t>29.05</t>
-        </is>
-      </c>
-      <c r="CI65" t="inlineStr">
-        <is>
-          <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
-        </is>
-      </c>
-      <c r="CJ65" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>【e】</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>1101</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>23375.276</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>21.2</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>5.99</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>2.43</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>6.09</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>-99.0</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>2025-02-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>2025-03-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>2024-11-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>2024-12-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q66" t="inlineStr">
-        <is>
-          <t>34.95</t>
-        </is>
-      </c>
-      <c r="R66" t="inlineStr">
-        <is>
-          <t>34.8</t>
-        </is>
-      </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>33.4</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>33.55</t>
-        </is>
-      </c>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W66" t="inlineStr">
-        <is>
-          <t>-39.08</t>
-        </is>
-      </c>
-      <c r="X66" t="inlineStr">
-        <is>
-          <t>4.17</t>
-        </is>
-      </c>
-      <c r="Y66" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>12.34</t>
-        </is>
-      </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>0.49</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr"/>
-      <c r="AD66" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="AE66" t="inlineStr">
-        <is>
-          <t>15342</t>
-        </is>
-      </c>
-      <c r="AF66" t="inlineStr">
-        <is>
-          <t>53.33</t>
-        </is>
-      </c>
-      <c r="AG66" t="inlineStr">
-        <is>
-          <t>34.89</t>
-        </is>
-      </c>
-      <c r="AH66" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AI66" t="n">
-        <v>-3.18</v>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>-4.49</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>-1.52</t>
-        </is>
-      </c>
-      <c r="AL66" t="inlineStr">
-        <is>
-          <t>20.81</t>
-        </is>
-      </c>
-      <c r="AM66" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="AN66" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>22.85</t>
-        </is>
-      </c>
-      <c r="AP66" t="inlineStr">
-        <is>
-          <t>-2.97</t>
-        </is>
-      </c>
-      <c r="AQ66" t="n">
-        <v>-0.48</v>
-      </c>
-      <c r="AR66" t="n">
-        <v>-0.47</v>
-      </c>
-      <c r="AS66" t="inlineStr">
-        <is>
-          <t>0.88</t>
-        </is>
-      </c>
-      <c r="AT66" t="inlineStr">
-        <is>
-          <t>-153.09</t>
-        </is>
-      </c>
-      <c r="AU66" t="inlineStr">
-        <is>
-          <t>2025/11/26</t>
-        </is>
-      </c>
-      <c r="AV66" t="inlineStr">
-        <is>
-          <t>991000616.0425532</t>
-        </is>
-      </c>
-      <c r="AW66" t="inlineStr">
-        <is>
-          <t>494560639.0</t>
-        </is>
-      </c>
-      <c r="AX66" t="n">
-        <v>640193393.2</v>
-      </c>
-      <c r="AY66" t="inlineStr">
-        <is>
-          <t>603452151.2</t>
-        </is>
-      </c>
-      <c r="AZ66" t="n">
-        <v>734438326</v>
-      </c>
-      <c r="BA66" t="inlineStr">
-        <is>
-          <t>36741242</t>
-        </is>
-      </c>
-      <c r="BB66" t="inlineStr">
-        <is>
-          <t>-554342.0861892588</t>
-        </is>
-      </c>
-      <c r="BC66" t="inlineStr">
-        <is>
-          <t>18609952.30385745</t>
-        </is>
-      </c>
-      <c r="BD66" t="inlineStr">
-        <is>
-          <t>494560639.0</t>
-        </is>
-      </c>
-      <c r="BE66" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF66" t="inlineStr">
-        <is>
-          <t>22.95</t>
-        </is>
-      </c>
-      <c r="BG66" t="inlineStr">
-        <is>
-          <t>2025/10/15</t>
-        </is>
-      </c>
-      <c r="BH66" t="inlineStr">
-        <is>
-          <t>-7.63</t>
-        </is>
-      </c>
-      <c r="BI66" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="BJ66" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="BK66" t="inlineStr">
-        <is>
-          <t>水泥工業</t>
-        </is>
-      </c>
-      <c r="BL66" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM66" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
-      </c>
-      <c r="BN66" t="inlineStr">
-        <is>
-          <t>4.325437847889285</t>
-        </is>
-      </c>
-      <c r="BO66" t="inlineStr">
-        <is>
-          <t>-14.68663446383302</t>
-        </is>
-      </c>
-      <c r="BP66" t="inlineStr">
-        <is>
-          <t>1.195709166622471</t>
-        </is>
-      </c>
-      <c r="BQ66" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR66" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS66" t="inlineStr">
-        <is>
-          <t>0.73</t>
-        </is>
-      </c>
-      <c r="BT66" t="inlineStr">
-        <is>
-          <t>4.43</t>
-        </is>
-      </c>
-      <c r="BU66" t="inlineStr">
-        <is>
-          <t>5.08</t>
-        </is>
-      </c>
-      <c r="BV66" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW66" t="inlineStr">
-        <is>
-          <t>22.64%</t>
-        </is>
-      </c>
-      <c r="BX66" t="inlineStr">
-        <is>
-          <t>13.16%</t>
-        </is>
-      </c>
-      <c r="BY66" t="inlineStr">
-        <is>
-          <t>20.16</t>
-        </is>
-      </c>
-      <c r="BZ66" t="inlineStr">
-        <is>
-          <t>170279</t>
-        </is>
-      </c>
-      <c r="CA66" t="inlineStr">
-        <is>
-          <t>水泥,預拌混擬土76.31%、電力供給及儲能,可充式鋰離20.52%、海陸運輸3.17% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB66" t="inlineStr">
-        <is>
-          <t>台泥-水泥工業-上市</t>
-        </is>
-      </c>
-      <c r="CC66" t="inlineStr">
-        <is>
-          <t>水泥工業右下上市</t>
-        </is>
-      </c>
-      <c r="CD66" t="inlineStr">
-        <is>
-          <t>21.3</t>
-        </is>
-      </c>
-      <c r="CE66" t="inlineStr">
-        <is>
-          <t>21.35</t>
-        </is>
-      </c>
-      <c r="CF66" t="inlineStr">
-        <is>
-          <t>20.95</t>
-        </is>
-      </c>
-      <c r="CG66" t="inlineStr">
-        <is>
-          <t>21.2</t>
-        </is>
-      </c>
-      <c r="CH66" t="inlineStr">
-        <is>
-          <t>29.05</t>
-        </is>
-      </c>
-      <c r="CI66" t="inlineStr">
-        <is>
-          <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
-        </is>
-      </c>
-      <c r="CJ66" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>【e】</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>1101</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>3.12</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>45105.494</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>21.2</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>5.99</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>2.43</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>12.57</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>-99.0</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>2025-02-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>2025-03-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>2024-11-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>2024-12-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>34.95</t>
-        </is>
-      </c>
-      <c r="R67" t="inlineStr">
-        <is>
-          <t>34.8</t>
-        </is>
-      </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>33.4</t>
-        </is>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>33.55</t>
-        </is>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>-39.08</t>
-        </is>
-      </c>
-      <c r="X67" t="inlineStr">
-        <is>
-          <t>4.17</t>
-        </is>
-      </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>23.81</t>
-        </is>
-      </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>1.22</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr"/>
-      <c r="AD67" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="AE67" t="inlineStr">
-        <is>
-          <t>15342</t>
-        </is>
-      </c>
-      <c r="AF67" t="inlineStr">
-        <is>
-          <t>43.24</t>
-        </is>
-      </c>
-      <c r="AG67" t="inlineStr">
-        <is>
-          <t>22.52</t>
-        </is>
-      </c>
-      <c r="AH67" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AI67" t="n">
-        <v>-3.86</v>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>-4.29</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>-1.56</t>
-        </is>
-      </c>
-      <c r="AL67" t="inlineStr">
-        <is>
-          <t>20.74</t>
-        </is>
-      </c>
-      <c r="AM67" t="n">
-        <v>21.57</v>
-      </c>
-      <c r="AN67" t="n">
-        <v>22.54</v>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>22.9</t>
-        </is>
-      </c>
-      <c r="AP67" t="inlineStr">
-        <is>
-          <t>-11.17</t>
-        </is>
-      </c>
-      <c r="AQ67" t="n">
-        <v>-0.52</v>
-      </c>
-      <c r="AR67" t="n">
-        <v>-0.46</v>
-      </c>
-      <c r="AS67" t="inlineStr">
-        <is>
-          <t>0.88</t>
-        </is>
-      </c>
-      <c r="AT67" t="inlineStr">
-        <is>
-          <t>-152.69</t>
-        </is>
-      </c>
-      <c r="AU67" t="inlineStr">
-        <is>
-          <t>2025/11/26</t>
-        </is>
-      </c>
-      <c r="AV67" t="inlineStr">
-        <is>
-          <t>991000616.0425532</t>
-        </is>
-      </c>
-      <c r="AW67" t="inlineStr">
-        <is>
-          <t>952963874.0</t>
-        </is>
-      </c>
-      <c r="AX67" t="n">
-        <v>684968154</v>
-      </c>
-      <c r="AY67" t="inlineStr">
-        <is>
-          <t>608460649.9</t>
-        </is>
-      </c>
-      <c r="AZ67" t="n">
-        <v>745292054.98</v>
-      </c>
-      <c r="BA67" t="inlineStr">
-        <is>
-          <t>76507504</t>
-        </is>
-      </c>
-      <c r="BB67" t="inlineStr">
-        <is>
-          <t>-4038759.248015933</t>
-        </is>
-      </c>
-      <c r="BC67" t="inlineStr">
-        <is>
-          <t>33234298.58837593</t>
-        </is>
-      </c>
-      <c r="BD67" t="inlineStr">
-        <is>
-          <t>952963874.0</t>
-        </is>
-      </c>
-      <c r="BE67" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF67" t="inlineStr">
-        <is>
-          <t>22.95</t>
-        </is>
-      </c>
-      <c r="BG67" t="inlineStr">
-        <is>
-          <t>2025/10/15</t>
-        </is>
-      </c>
-      <c r="BH67" t="inlineStr">
-        <is>
-          <t>-7.63</t>
-        </is>
-      </c>
-      <c r="BI67" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="BJ67" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="BK67" t="inlineStr">
-        <is>
-          <t>水泥工業</t>
-        </is>
-      </c>
-      <c r="BL67" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM67" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
-      </c>
-      <c r="BN67" t="inlineStr">
-        <is>
-          <t>4.325437847889285</t>
-        </is>
-      </c>
-      <c r="BO67" t="inlineStr">
-        <is>
-          <t>-14.68663446383302</t>
-        </is>
-      </c>
-      <c r="BP67" t="inlineStr">
-        <is>
-          <t>1.195709166622471</t>
-        </is>
-      </c>
-      <c r="BQ67" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR67" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS67" t="inlineStr">
-        <is>
-          <t>0.73</t>
-        </is>
-      </c>
-      <c r="BT67" t="inlineStr">
-        <is>
-          <t>4.43</t>
-        </is>
-      </c>
-      <c r="BU67" t="inlineStr">
-        <is>
-          <t>5.08</t>
-        </is>
-      </c>
-      <c r="BV67" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW67" t="inlineStr">
-        <is>
-          <t>22.64%</t>
-        </is>
-      </c>
-      <c r="BX67" t="inlineStr">
-        <is>
-          <t>13.16%</t>
-        </is>
-      </c>
-      <c r="BY67" t="inlineStr">
-        <is>
-          <t>20.16</t>
-        </is>
-      </c>
-      <c r="BZ67" t="inlineStr">
-        <is>
-          <t>170279</t>
-        </is>
-      </c>
-      <c r="CA67" t="inlineStr">
-        <is>
-          <t>水泥,預拌混擬土76.31%、電力供給及儲能,可充式鋰離20.52%、海陸運輸3.17% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB67" t="inlineStr">
-        <is>
-          <t>台泥-水泥工業-上市</t>
-        </is>
-      </c>
-      <c r="CC67" t="inlineStr">
-        <is>
-          <t>水泥工業右下上市</t>
-        </is>
-      </c>
-      <c r="CD67" t="inlineStr">
-        <is>
-          <t>20.8</t>
-        </is>
-      </c>
-      <c r="CE67" t="inlineStr">
-        <is>
-          <t>21.35</t>
-        </is>
-      </c>
-      <c r="CF67" t="inlineStr">
-        <is>
-          <t>20.8</t>
-        </is>
-      </c>
-      <c r="CG67" t="inlineStr">
-        <is>
-          <t>21.2</t>
-        </is>
-      </c>
-      <c r="CH67" t="inlineStr">
-        <is>
-          <t>29.05</t>
-        </is>
-      </c>
-      <c r="CI67" t="inlineStr">
-        <is>
-          <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
-        </is>
-      </c>
-      <c r="CJ67" t="inlineStr">
         <is>
           <t>True</t>
         </is>
